--- a/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3292BCB8-7442-43D7-87A0-C5D83D63794B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E94C25-F818-436C-9BBB-06282A2E6B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="EOS" sheetId="5" r:id="rId1"/>
@@ -703,10 +703,10 @@
     <t>Table 7.2.7 Exports of Services</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -756,10 +756,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1236,7 +1238,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1246,7 +1248,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2024,28 +2026,28 @@
         <v>61672.955299723086</v>
       </c>
       <c r="CT12" s="15">
-        <v>102551.04168472652</v>
+        <v>100946.55462321846</v>
       </c>
       <c r="CU12" s="15">
-        <v>37899.759232198536</v>
+        <v>36463.105749075425</v>
       </c>
       <c r="CV12" s="15">
-        <v>47076.570242629052</v>
+        <v>44249.13574726443</v>
       </c>
       <c r="CW12" s="15">
-        <v>59796.72855013558</v>
+        <v>58266.301089199689</v>
       </c>
       <c r="CX12" s="15">
-        <v>113547.93297508758</v>
+        <v>106688.73101515614</v>
       </c>
       <c r="CY12" s="15">
-        <v>39112.034454226137</v>
+        <v>36792.590610911582</v>
       </c>
       <c r="CZ12" s="15">
-        <v>48050.318323695501</v>
+        <v>44641.263035980199</v>
       </c>
       <c r="DA12" s="15">
-        <v>65350.491897018961</v>
+        <v>61885.180174758614</v>
       </c>
       <c r="DB12" s="7"/>
       <c r="DC12" s="7"/>
@@ -2415,28 +2417,28 @@
         <v>928.65521148485902</v>
       </c>
       <c r="CT13" s="15">
-        <v>551.83299585022792</v>
+        <v>552.18643430327757</v>
       </c>
       <c r="CU13" s="15">
-        <v>493.22468399087808</v>
+        <v>493.79640081665167</v>
       </c>
       <c r="CV13" s="15">
         <v>958.26713790390681</v>
       </c>
       <c r="CW13" s="15">
-        <v>863.38954187903425</v>
+        <v>864.4719301162844</v>
       </c>
       <c r="CX13" s="15">
-        <v>626.54657634907812</v>
+        <v>610.60236568850678</v>
       </c>
       <c r="CY13" s="15">
-        <v>554.44115787790076</v>
+        <v>564.89073113456982</v>
       </c>
       <c r="CZ13" s="15">
-        <v>1070.9503659927748</v>
+        <v>1084.6375557569775</v>
       </c>
       <c r="DA13" s="15">
-        <v>976.88167464358264</v>
+        <v>1080.6764549816762</v>
       </c>
       <c r="DB13" s="7"/>
       <c r="DC13" s="7"/>
@@ -3585,7 +3587,7 @@
         <v>90834.805619856139</v>
       </c>
       <c r="CS16" s="15">
-        <v>100998.99676650774</v>
+        <v>100998.996766508</v>
       </c>
       <c r="CT16" s="15">
         <v>145409.2234306508</v>
@@ -3609,7 +3611,7 @@
         <v>109678.24932371668</v>
       </c>
       <c r="DA16" s="15">
-        <v>136103.15153939478</v>
+        <v>134941.74006719203</v>
       </c>
       <c r="DB16" s="7"/>
       <c r="DC16" s="7"/>
@@ -3988,19 +3990,19 @@
         <v>379770.97859428002</v>
       </c>
       <c r="CW17" s="15">
-        <v>430739.22646283725</v>
+        <v>430747.10598567297</v>
       </c>
       <c r="CX17" s="15">
-        <v>502337.73794255027</v>
+        <v>503163.39248795487</v>
       </c>
       <c r="CY17" s="15">
-        <v>475531.27395853889</v>
+        <v>473958.23665461061</v>
       </c>
       <c r="CZ17" s="15">
-        <v>403264.62587894895</v>
+        <v>403281.33118773223</v>
       </c>
       <c r="DA17" s="15">
-        <v>457577.78325732553</v>
+        <v>453711.15566789632</v>
       </c>
       <c r="DB17" s="7"/>
       <c r="DC17" s="7"/>
@@ -4370,28 +4372,28 @@
         <v>67044.588788803754</v>
       </c>
       <c r="CT18" s="15">
-        <v>69058.861696831635</v>
+        <v>69237.372353962972</v>
       </c>
       <c r="CU18" s="15">
-        <v>85045.833458954265</v>
+        <v>85293.61065593797</v>
       </c>
       <c r="CV18" s="15">
-        <v>69245.625787716475</v>
+        <v>69345.660940323476</v>
       </c>
       <c r="CW18" s="15">
-        <v>70364.091050420931</v>
+        <v>70046.973827350899</v>
       </c>
       <c r="CX18" s="15">
-        <v>77066.616276855959</v>
+        <v>79290.862408096873</v>
       </c>
       <c r="CY18" s="15">
-        <v>77174.591328196519</v>
+        <v>75216.454959103881</v>
       </c>
       <c r="CZ18" s="15">
-        <v>66803.789183967019</v>
+        <v>65545.176611603965</v>
       </c>
       <c r="DA18" s="15">
-        <v>71951.110671672766</v>
+        <v>73578.480825932318</v>
       </c>
       <c r="DB18" s="7"/>
       <c r="DC18" s="7"/>
@@ -4761,28 +4763,28 @@
         <v>12681.475726949</v>
       </c>
       <c r="CT19" s="15">
-        <v>9669.8646705007523</v>
+        <v>9385.2576524775213</v>
       </c>
       <c r="CU19" s="15">
-        <v>17165.298383690697</v>
+        <v>15177.018101764188</v>
       </c>
       <c r="CV19" s="15">
-        <v>11149.028075453512</v>
+        <v>10975.702627120954</v>
       </c>
       <c r="CW19" s="15">
-        <v>15970.597082653281</v>
+        <v>15137.743429370686</v>
       </c>
       <c r="CX19" s="15">
-        <v>14612.048770540849</v>
+        <v>11669.687581209831</v>
       </c>
       <c r="CY19" s="15">
-        <v>16630.749970385208</v>
+        <v>14892.20405974895</v>
       </c>
       <c r="CZ19" s="15">
-        <v>13111.392106418116</v>
+        <v>11858.652827870021</v>
       </c>
       <c r="DA19" s="15">
-        <v>18743.072017771967</v>
+        <v>17917.920810125586</v>
       </c>
       <c r="DB19" s="7"/>
       <c r="DC19" s="7"/>
@@ -5329,31 +5331,31 @@
         <v>740161.4618690979</v>
       </c>
       <c r="CS21" s="14">
-        <v>714994.55963249772</v>
+        <v>714994.55963249796</v>
       </c>
       <c r="CT21" s="14">
-        <v>971133.19669752906</v>
+        <v>969422.96671358217</v>
       </c>
       <c r="CU21" s="14">
-        <v>920885.80877375999</v>
+        <v>917709.22392251983</v>
       </c>
       <c r="CV21" s="14">
-        <v>766290.61397139379</v>
+        <v>763389.88918030378</v>
       </c>
       <c r="CW21" s="14">
-        <v>817284.55070176069</v>
+        <v>814613.11427554523</v>
       </c>
       <c r="CX21" s="14">
-        <v>1049076.8223419285</v>
+        <v>1042309.2156586511</v>
       </c>
       <c r="CY21" s="14">
-        <v>897348.56774286565</v>
+        <v>889769.85388915043</v>
       </c>
       <c r="CZ21" s="14">
-        <v>785953.93097019987</v>
+        <v>780063.91633012088</v>
       </c>
       <c r="DA21" s="14">
-        <v>852735.65447893133</v>
+        <v>845148.31742199033</v>
       </c>
       <c r="DB21" s="7"/>
       <c r="DC21" s="7"/>
@@ -5914,7 +5916,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5924,7 +5926,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6702,28 +6704,28 @@
         <v>45286.029744744272</v>
       </c>
       <c r="CT37" s="15">
-        <v>73659.398118893834</v>
+        <v>72506.942236450675</v>
       </c>
       <c r="CU37" s="15">
-        <v>26785.035407387935</v>
+        <v>25769.704038715077</v>
       </c>
       <c r="CV37" s="15">
-        <v>36166.174066956592</v>
+        <v>33994.021601404245</v>
       </c>
       <c r="CW37" s="15">
-        <v>44471.125472640255</v>
+        <v>43332.938931465338</v>
       </c>
       <c r="CX37" s="15">
-        <v>79561.871923792613</v>
+        <v>74755.699468366016</v>
       </c>
       <c r="CY37" s="15">
-        <v>27571.022589854354</v>
+        <v>25935.990316737345</v>
       </c>
       <c r="CZ37" s="15">
-        <v>37071.109093012972</v>
+        <v>34441.002469709194</v>
       </c>
       <c r="DA37" s="15">
-        <v>48127.073632377091</v>
+        <v>45575.060517017955</v>
       </c>
       <c r="DB37" s="7"/>
       <c r="DC37" s="7"/>
@@ -7093,28 +7095,28 @@
         <v>788.1715358955704</v>
       </c>
       <c r="CT38" s="15">
-        <v>451.27257136007933</v>
+        <v>451.56160278937887</v>
       </c>
       <c r="CU38" s="15">
-        <v>403.79225281917155</v>
+        <v>404.26030487039048</v>
       </c>
       <c r="CV38" s="15">
         <v>776.88441164857181</v>
       </c>
       <c r="CW38" s="15">
-        <v>717.62271416422254</v>
+        <v>718.52236182836305</v>
       </c>
       <c r="CX38" s="15">
-        <v>503.49391499310173</v>
+        <v>490.68111966391115</v>
       </c>
       <c r="CY38" s="15">
-        <v>446.32229880937172</v>
+        <v>454.73415188201199</v>
       </c>
       <c r="CZ38" s="15">
-        <v>853.35741945352277</v>
+        <v>864.26368113253454</v>
       </c>
       <c r="DA38" s="15">
-        <v>794.22988529340591</v>
+        <v>878.61770689120135</v>
       </c>
       <c r="DB38" s="7"/>
       <c r="DC38" s="7"/>
@@ -8287,7 +8289,7 @@
         <v>104398.43912754364</v>
       </c>
       <c r="DA41" s="15">
-        <v>129746.56233296984</v>
+        <v>128639.39365782891</v>
       </c>
       <c r="DB41" s="7"/>
       <c r="DC41" s="7"/>
@@ -8666,19 +8668,19 @@
         <v>308215.00180056016</v>
       </c>
       <c r="CW42" s="15">
-        <v>350318.23129018105</v>
+        <v>350324.61593015492</v>
       </c>
       <c r="CX42" s="15">
-        <v>408875.61114876601</v>
+        <v>409547.45563269104</v>
       </c>
       <c r="CY42" s="15">
-        <v>384215.64397013263</v>
+        <v>382944.67490076588</v>
       </c>
       <c r="CZ42" s="15">
-        <v>321689.31316797069</v>
+        <v>321702.69942801312</v>
       </c>
       <c r="DA42" s="15">
-        <v>364022.40528213762</v>
+        <v>360931.83322930959</v>
       </c>
       <c r="DB42" s="7"/>
       <c r="DC42" s="7"/>
@@ -9048,28 +9050,28 @@
         <v>55989.920236420461</v>
       </c>
       <c r="CT43" s="15">
-        <v>55875.772272099697</v>
+        <v>56020.205883962597</v>
       </c>
       <c r="CU43" s="15">
-        <v>69679.751388542558</v>
+        <v>69882.760199008349</v>
       </c>
       <c r="CV43" s="15">
-        <v>55615.240244920344</v>
+        <v>55695.584367482421</v>
       </c>
       <c r="CW43" s="15">
-        <v>57546.689590979142</v>
+        <v>57287.33789428931</v>
       </c>
       <c r="CX43" s="15">
-        <v>61274.532486071264</v>
+        <v>63042.997852918685</v>
       </c>
       <c r="CY43" s="15">
-        <v>62173.860384176871</v>
+        <v>60596.334735775235</v>
       </c>
       <c r="CZ43" s="15">
-        <v>52734.445393829716</v>
+        <v>51740.905404855606</v>
       </c>
       <c r="DA43" s="15">
-        <v>57560.112652476433</v>
+        <v>58861.991227136663</v>
       </c>
       <c r="DB43" s="7"/>
       <c r="DC43" s="7"/>
@@ -9439,28 +9441,28 @@
         <v>10777.035572764122</v>
       </c>
       <c r="CT44" s="15">
-        <v>7941.4464011707541</v>
+        <v>7708.9600019018644</v>
       </c>
       <c r="CU44" s="15">
-        <v>14128.015715401656</v>
+        <v>12491.548090908125</v>
       </c>
       <c r="CV44" s="15">
-        <v>9326.2981914489246</v>
+        <v>9181.3093364226297</v>
       </c>
       <c r="CW44" s="15">
-        <v>13291.494658381971</v>
+        <v>12598.354018333939</v>
       </c>
       <c r="CX44" s="15">
-        <v>11772.064326063968</v>
+        <v>9410.6946429814798</v>
       </c>
       <c r="CY44" s="15">
-        <v>13459.272650343211</v>
+        <v>12052.266744532541</v>
       </c>
       <c r="CZ44" s="15">
-        <v>10783.634886690787</v>
+        <v>9753.1704807203023</v>
       </c>
       <c r="DA44" s="15">
-        <v>15322.799317707944</v>
+        <v>14648.389538574198</v>
       </c>
       <c r="DB44" s="7"/>
       <c r="DC44" s="7"/>
@@ -10010,28 +10012,28 @@
         <v>600657.65527532401</v>
       </c>
       <c r="CT46" s="14">
-        <v>806614.77852686064</v>
+        <v>805374.55888844072</v>
       </c>
       <c r="CU46" s="14">
-        <v>766584.1199400723</v>
+        <v>764135.79780942295</v>
       </c>
       <c r="CV46" s="14">
-        <v>632967.58104178857</v>
+        <v>630730.7838437719</v>
       </c>
       <c r="CW46" s="14">
-        <v>680010.80120309908</v>
+        <v>677927.40661282418</v>
       </c>
       <c r="CX46" s="14">
-        <v>857097.21772260277</v>
+        <v>852357.1726395369</v>
       </c>
       <c r="CY46" s="14">
-        <v>736799.28113052133</v>
+        <v>730917.1600868979</v>
       </c>
       <c r="CZ46" s="14">
-        <v>640385.91794676485</v>
+        <v>635756.09945023805</v>
       </c>
       <c r="DA46" s="14">
-        <v>697230.306294473</v>
+        <v>691192.40906826931</v>
       </c>
       <c r="DB46" s="7"/>
       <c r="DC46" s="7"/>
@@ -10592,7 +10594,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:179" x14ac:dyDescent="0.2">
@@ -10614,7 +10616,7 @@
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CS56" s="23"/>
       <c r="CW56" s="23"/>
@@ -11386,28 +11388,28 @@
         <v>13.067038716920834</v>
       </c>
       <c r="CP62" s="27">
-        <v>11.921143386139548</v>
+        <v>10.170054138072018</v>
       </c>
       <c r="CQ62" s="27">
-        <v>8.4269041938107563</v>
+        <v>4.3168018414466047</v>
       </c>
       <c r="CR62" s="27">
-        <v>-9.7537261567932063</v>
+        <v>-15.17394743517653</v>
       </c>
       <c r="CS62" s="27">
-        <v>-3.042219625230004</v>
+        <v>-5.5237408260516645</v>
       </c>
       <c r="CT62" s="27">
-        <v>10.72333455584868</v>
+        <v>5.6883332109454159</v>
       </c>
       <c r="CU62" s="27">
-        <v>3.1986356815630899</v>
+        <v>0.90361162349566371</v>
       </c>
       <c r="CV62" s="27">
-        <v>2.068434629047573</v>
+        <v>0.88618067244401288</v>
       </c>
       <c r="CW62" s="27">
-        <v>9.2877377768700455</v>
+        <v>6.2109298478013812</v>
       </c>
       <c r="CX62" s="28"/>
       <c r="CY62" s="28"/>
@@ -11765,28 +11767,28 @@
         <v>-7.175047970254866</v>
       </c>
       <c r="CP63" s="27">
-        <v>14.213060480499863</v>
+        <v>14.286211755827466</v>
       </c>
       <c r="CQ63" s="27">
-        <v>3.2443460171701872</v>
+        <v>3.3640207449360418</v>
       </c>
       <c r="CR63" s="27">
         <v>3.6415975432381202</v>
       </c>
       <c r="CS63" s="27">
-        <v>-7.0279764544118848</v>
+        <v>-6.9114220837623606</v>
       </c>
       <c r="CT63" s="27">
-        <v>13.539165120733031</v>
+        <v>10.579023271177547</v>
       </c>
       <c r="CU63" s="27">
-        <v>12.411478150626152</v>
+        <v>14.397498685762145</v>
       </c>
       <c r="CV63" s="27">
-        <v>11.759062127012811</v>
+        <v>13.187389283690834</v>
       </c>
       <c r="CW63" s="27">
-        <v>13.144951063172499</v>
+        <v>25.010011005945444</v>
       </c>
       <c r="CX63" s="28"/>
       <c r="CY63" s="28"/>
@@ -12911,7 +12913,7 @@
         <v>13.54658869242455</v>
       </c>
       <c r="CS66" s="27">
-        <v>26.632341539205669</v>
+        <v>26.632341539205328</v>
       </c>
       <c r="CT66" s="27">
         <v>20.281182792177944</v>
@@ -12923,7 +12925,7 @@
         <v>6.339380850925707</v>
       </c>
       <c r="CW66" s="27">
-        <v>6.4158906697003459</v>
+        <v>5.5078100348982133</v>
       </c>
       <c r="CX66" s="28"/>
       <c r="CY66" s="28"/>
@@ -13290,19 +13292,19 @@
         <v>12.23312443344517</v>
       </c>
       <c r="CS67" s="27">
-        <v>20.091629022547266</v>
+        <v>20.093825861551309</v>
       </c>
       <c r="CT67" s="27">
-        <v>3.0553576107515568</v>
+        <v>3.2247419074363108</v>
       </c>
       <c r="CU67" s="27">
-        <v>1.859328539977696</v>
+        <v>1.5223821973898453</v>
       </c>
       <c r="CV67" s="27">
-        <v>6.1862671475399651</v>
+        <v>6.1906659325248228</v>
       </c>
       <c r="CW67" s="27">
-        <v>6.2308132497897333</v>
+        <v>5.3312139218381986</v>
       </c>
       <c r="CX67" s="28"/>
       <c r="CY67" s="28"/>
@@ -13660,28 +13662,28 @@
         <v>0.48861261138691248</v>
       </c>
       <c r="CP68" s="27">
-        <v>8.3294940811998117</v>
+        <v>8.6095156265886317</v>
       </c>
       <c r="CQ68" s="27">
-        <v>8.5722774120493597</v>
+        <v>8.8885978415537323</v>
       </c>
       <c r="CR68" s="27">
-        <v>0.32863833987977387</v>
+        <v>0.47357732386630857</v>
       </c>
       <c r="CS68" s="27">
-        <v>4.9511859518952264</v>
+        <v>4.4781914436151169</v>
       </c>
       <c r="CT68" s="27">
-        <v>11.595549627183786</v>
+        <v>14.520322930132792</v>
       </c>
       <c r="CU68" s="27">
-        <v>-9.2552942461980194</v>
+        <v>-11.814666560997011</v>
       </c>
       <c r="CV68" s="27">
-        <v>-3.5263405824871796</v>
+        <v>-5.4804933389993664</v>
       </c>
       <c r="CW68" s="27">
-        <v>2.2554396675352706</v>
+        <v>5.0416267907386469</v>
       </c>
       <c r="CX68" s="28"/>
       <c r="CY68" s="28"/>
@@ -14039,28 +14041,28 @@
         <v>15.029482963772594</v>
       </c>
       <c r="CP69" s="27">
-        <v>3.4387205001434182</v>
+        <v>0.39427398586147433</v>
       </c>
       <c r="CQ69" s="27">
-        <v>50.343591679616196</v>
+        <v>32.929085262727483</v>
       </c>
       <c r="CR69" s="27">
-        <v>24.500626100976092</v>
+        <v>22.565109687294608</v>
       </c>
       <c r="CS69" s="27">
-        <v>25.936424328871084</v>
+        <v>19.368942190236965</v>
       </c>
       <c r="CT69" s="27">
-        <v>51.109134082474867</v>
+        <v>24.340620293245394</v>
       </c>
       <c r="CU69" s="27">
-        <v>-3.1141224659012039</v>
+        <v>-1.8766139705804932</v>
       </c>
       <c r="CV69" s="27">
-        <v>17.601211672298888</v>
+        <v>8.0445893146494001</v>
       </c>
       <c r="CW69" s="27">
-        <v>17.35987027141303</v>
+        <v>18.365864065054225</v>
       </c>
       <c r="CX69" s="28"/>
       <c r="CY69" s="28"/>
@@ -14594,28 +14596,28 @@
         <v>15.126032923892183</v>
       </c>
       <c r="CP71" s="27">
-        <v>11.235395399147635</v>
+        <v>11.039502488541018</v>
       </c>
       <c r="CQ71" s="27">
-        <v>10.021160966528967</v>
+        <v>9.6416442556487141</v>
       </c>
       <c r="CR71" s="27">
-        <v>3.5301962407382064</v>
+        <v>3.1382919143815116</v>
       </c>
       <c r="CS71" s="27">
-        <v>14.306401313296618</v>
+        <v>13.932770998180814</v>
       </c>
       <c r="CT71" s="27">
-        <v>8.0260489405014113</v>
+        <v>7.5185188970877022</v>
       </c>
       <c r="CU71" s="27">
-        <v>-2.5559348191320623</v>
+        <v>-3.0444686949913802</v>
       </c>
       <c r="CV71" s="27">
-        <v>2.5660391293191651</v>
+        <v>2.1842085395866349</v>
       </c>
       <c r="CW71" s="27">
-        <v>4.3376696337561498</v>
+        <v>3.7484300966110595</v>
       </c>
       <c r="CX71" s="28"/>
       <c r="CY71" s="28"/>
@@ -15180,7 +15182,7 @@
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CX78" s="24"/>
       <c r="CY78" s="24"/>
@@ -15204,7 +15206,7 @@
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CX81" s="24"/>
       <c r="CY81" s="24"/>
@@ -15978,28 +15980,28 @@
         <v>10.449033189560922</v>
       </c>
       <c r="CP87" s="27">
-        <v>9.9137595667386336</v>
+        <v>8.1940773264673794</v>
       </c>
       <c r="CQ87" s="27">
-        <v>8.5500306008896843</v>
+        <v>4.4352609370391605</v>
       </c>
       <c r="CR87" s="27">
-        <v>-9.674327918296143</v>
+        <v>-15.099317881340255</v>
       </c>
       <c r="CS87" s="27">
-        <v>-1.7994606210728676</v>
+        <v>-4.3127887878172828</v>
       </c>
       <c r="CT87" s="27">
-        <v>8.0131985267807693</v>
+        <v>3.1014371349187115</v>
       </c>
       <c r="CU87" s="27">
-        <v>2.9344265203010451</v>
+        <v>0.64527818314267904</v>
       </c>
       <c r="CV87" s="27">
-        <v>2.5021585760800065</v>
+        <v>1.3148808150621534</v>
       </c>
       <c r="CW87" s="27">
-        <v>8.2209481340562434</v>
+        <v>5.1741738290558033</v>
       </c>
       <c r="CX87" s="28"/>
       <c r="CY87" s="28"/>
@@ -16357,28 +16359,28 @@
         <v>-9.8583317600556768</v>
       </c>
       <c r="CP88" s="27">
-        <v>11.698478325473033</v>
+        <v>11.770019059144701</v>
       </c>
       <c r="CQ88" s="27">
-        <v>0.81038995601862496</v>
+        <v>0.92724338615175839</v>
       </c>
       <c r="CR88" s="27">
         <v>0.84437002222807678</v>
       </c>
       <c r="CS88" s="27">
-        <v>-8.95094767044408</v>
+        <v>-8.8368040325216128</v>
       </c>
       <c r="CT88" s="27">
-        <v>11.572018098869563</v>
+        <v>8.6631628182918661</v>
       </c>
       <c r="CU88" s="27">
-        <v>10.532655268462079</v>
+        <v>12.485481855015152</v>
       </c>
       <c r="CV88" s="27">
-        <v>9.8435502963269528</v>
+        <v>11.247396417510984</v>
       </c>
       <c r="CW88" s="27">
-        <v>10.675131878790054</v>
+        <v>22.281191730130317</v>
       </c>
       <c r="CX88" s="28"/>
       <c r="CY88" s="28"/>
@@ -17515,7 +17517,7 @@
         <v>4.5167604905628025</v>
       </c>
       <c r="CW91" s="27">
-        <v>5.6968643813915634</v>
+        <v>4.794919426554344</v>
       </c>
       <c r="CX91" s="28"/>
       <c r="CY91" s="28"/>
@@ -17843,19 +17845,19 @@
         <v>9.2230669843617079</v>
       </c>
       <c r="CS92" s="27">
-        <v>17.634565988506836</v>
+        <v>17.636709908763422</v>
       </c>
       <c r="CT92" s="27">
-        <v>1.270888816869757</v>
+        <v>1.4372922074819883</v>
       </c>
       <c r="CU92" s="27">
-        <v>0.15687216833970297</v>
+        <v>-0.17444252071125277</v>
       </c>
       <c r="CV92" s="27">
-        <v>4.3717247014892138</v>
+        <v>4.3760678580404146</v>
       </c>
       <c r="CW92" s="27">
-        <v>3.911921438255078</v>
+        <v>3.0278252845553624</v>
       </c>
       <c r="CX92" s="28"/>
       <c r="CY92" s="28"/>
@@ -18174,28 +18176,28 @@
         <v>-1.1499697637559763</v>
       </c>
       <c r="CP93" s="27">
-        <v>5.9444479968583153</v>
+        <v>6.2183044226181465</v>
       </c>
       <c r="CQ93" s="27">
-        <v>6.0127168852565802</v>
+        <v>6.3215801506995888</v>
       </c>
       <c r="CR93" s="27">
-        <v>-2.3791743044852751</v>
+        <v>-2.2381471408921527</v>
       </c>
       <c r="CS93" s="27">
-        <v>2.7804457444931927</v>
+        <v>2.3172343385924279</v>
       </c>
       <c r="CT93" s="27">
-        <v>9.662077130104052</v>
+        <v>12.536176649373161</v>
       </c>
       <c r="CU93" s="27">
-        <v>-10.771983043555863</v>
+        <v>-13.288578523211925</v>
       </c>
       <c r="CV93" s="27">
-        <v>-5.1798658756198535</v>
+        <v>-7.1005251269717036</v>
       </c>
       <c r="CW93" s="27">
-        <v>2.3325514625938126E-2</v>
+        <v>2.748693499692763</v>
       </c>
       <c r="CX93" s="28"/>
       <c r="CY93" s="28"/>
@@ -18553,28 +18555,28 @@
         <v>11.704334496289917</v>
       </c>
       <c r="CP94" s="27">
-        <v>1.2543637257587505</v>
+        <v>-1.7098648597787331</v>
       </c>
       <c r="CQ94" s="27">
-        <v>46.799284312285465</v>
+        <v>29.79531992583685</v>
       </c>
       <c r="CR94" s="27">
-        <v>21.140425313185787</v>
+        <v>19.257147382006053</v>
       </c>
       <c r="CS94" s="27">
-        <v>23.331639472105167</v>
+        <v>16.899994745982653</v>
       </c>
       <c r="CT94" s="27">
-        <v>48.235771311489202</v>
+        <v>22.074762881890479</v>
       </c>
       <c r="CU94" s="27">
-        <v>-4.7334535757163252</v>
+        <v>-3.5166285489891607</v>
       </c>
       <c r="CV94" s="27">
-        <v>15.626100145265156</v>
+        <v>6.2285358584867225</v>
       </c>
       <c r="CW94" s="27">
-        <v>15.282740666377777</v>
+        <v>16.272248876773233</v>
       </c>
       <c r="CX94" s="28"/>
       <c r="CY94" s="28"/>
@@ -19108,28 +19110,28 @@
         <v>12.261066393324938</v>
       </c>
       <c r="CP96" s="27">
-        <v>8.9640128005354001</v>
+        <v>8.7964739552850517</v>
       </c>
       <c r="CQ96" s="27">
-        <v>7.6052672868729587</v>
+        <v>7.2615967745050654</v>
       </c>
       <c r="CR96" s="27">
-        <v>1.9765734484086011</v>
+        <v>1.6162059973974294</v>
       </c>
       <c r="CS96" s="27">
-        <v>13.211043800216274</v>
+        <v>12.864191550523387</v>
       </c>
       <c r="CT96" s="27">
-        <v>6.2585561955533962</v>
+        <v>5.8336351989986497</v>
       </c>
       <c r="CU96" s="27">
-        <v>-3.8853973145020859</v>
+        <v>-4.3472165311132045</v>
       </c>
       <c r="CV96" s="27">
-        <v>1.1719931837214546</v>
+        <v>0.79674494018526332</v>
       </c>
       <c r="CW96" s="27">
-        <v>2.5322399380875282</v>
+        <v>1.9566995412859853</v>
       </c>
       <c r="CX96" s="28"/>
       <c r="CY96" s="28"/>
@@ -19681,7 +19683,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19691,7 +19693,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -20472,10 +20474,10 @@
         <v>139.22329574183948</v>
       </c>
       <c r="CU111" s="27">
-        <v>141.49602065392418</v>
+        <v>141.49602065392421</v>
       </c>
       <c r="CV111" s="27">
-        <v>130.16740492227183</v>
+        <v>130.16740492227186</v>
       </c>
       <c r="CW111" s="27">
         <v>134.46191863735046</v>
@@ -20487,7 +20489,7 @@
         <v>141.85920861933744</v>
       </c>
       <c r="CZ111" s="27">
-        <v>129.61661924690526</v>
+        <v>129.61661924690523</v>
       </c>
       <c r="DA111" s="27">
         <v>135.78737904615701</v>
@@ -22030,7 +22032,7 @@
         <v>102.55633330527829</v>
       </c>
       <c r="CS115" s="27">
-        <v>103.68565782484302</v>
+        <v>103.68565782484329</v>
       </c>
       <c r="CT115" s="27">
         <v>103.4351367474827</v>
@@ -22433,19 +22435,19 @@
         <v>123.21625371110987</v>
       </c>
       <c r="CW116" s="27">
-        <v>122.95655435244552</v>
+        <v>122.9565626845794</v>
       </c>
       <c r="CX116" s="27">
-        <v>122.85832762956821</v>
+        <v>122.85838565658793</v>
       </c>
       <c r="CY116" s="27">
-        <v>123.76676520633939</v>
+        <v>123.7667652063394</v>
       </c>
       <c r="CZ116" s="27">
-        <v>125.35841551826235</v>
+        <v>125.35839205103525</v>
       </c>
       <c r="DA116" s="27">
-        <v>125.70044497746706</v>
+        <v>125.7054972426446</v>
       </c>
       <c r="DB116" s="7"/>
       <c r="DC116" s="7"/>
@@ -23206,28 +23208,28 @@
         <v>117.67128020805468</v>
       </c>
       <c r="CT118" s="27">
-        <v>121.76452729159249</v>
+        <v>121.74479631704018</v>
       </c>
       <c r="CU118" s="27">
         <v>121.49829621846999</v>
       </c>
       <c r="CV118" s="27">
-        <v>119.543980329471</v>
+        <v>119.54398032947103</v>
       </c>
       <c r="CW118" s="27">
         <v>120.15651733028984</v>
       </c>
       <c r="CX118" s="27">
-        <v>124.12477850795469</v>
+        <v>124.00452914401079</v>
       </c>
       <c r="CY118" s="27">
         <v>123.56351195516591</v>
       </c>
       <c r="CZ118" s="27">
-        <v>121.58601662784649</v>
+        <v>121.58767091492717</v>
       </c>
       <c r="DA118" s="27">
-        <v>122.32146117133669</v>
+        <v>122.32007322676392</v>
       </c>
       <c r="DB118" s="7"/>
       <c r="DC118" s="7"/>
@@ -23774,31 +23776,31 @@
         <v>119.2464384285621</v>
       </c>
       <c r="CS120" s="27">
-        <v>119.03528629877613</v>
+        <v>119.03528629877617</v>
       </c>
       <c r="CT120" s="27">
-        <v>120.39615719304477</v>
+        <v>120.36920660264676</v>
       </c>
       <c r="CU120" s="27">
-        <v>120.12847446484413</v>
+        <v>120.09766150903434</v>
       </c>
       <c r="CV120" s="27">
-        <v>121.06316925586798</v>
+        <v>121.03260356630869</v>
       </c>
       <c r="CW120" s="27">
-        <v>120.18699545004168</v>
+        <v>120.16229264806586</v>
       </c>
       <c r="CX120" s="27">
-        <v>122.39881318591088</v>
+        <v>122.2854982766063</v>
       </c>
       <c r="CY120" s="27">
-        <v>121.79009816160551</v>
+        <v>121.73333757595275</v>
       </c>
       <c r="CZ120" s="27">
-        <v>122.73129513687027</v>
+        <v>122.69861303803002</v>
       </c>
       <c r="DA120" s="27">
-        <v>122.30329731518887</v>
+        <v>122.27395821103624</v>
       </c>
       <c r="DB120" s="7"/>
       <c r="DC120" s="7"/>
@@ -23999,7 +24001,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24009,7 +24011,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24784,31 +24786,31 @@
         <v>7.0477268960050496</v>
       </c>
       <c r="CS136" s="17">
-        <v>8.6256537855927959</v>
+        <v>8.6256537855927942</v>
       </c>
       <c r="CT136" s="17">
-        <v>10.55993575685244</v>
+        <v>10.413055816640592</v>
       </c>
       <c r="CU136" s="17">
-        <v>4.1155764233858028</v>
+        <v>3.973274409646113</v>
       </c>
       <c r="CV136" s="17">
-        <v>6.1434355823111328</v>
+        <v>5.7964005515945862</v>
       </c>
       <c r="CW136" s="17">
-        <v>7.3165127737690838</v>
+        <v>7.1526347990379824</v>
       </c>
       <c r="CX136" s="17">
-        <v>10.823605150441365</v>
+        <v>10.235804251978902</v>
       </c>
       <c r="CY136" s="17">
-        <v>4.3586222634317116</v>
+        <v>4.1350682370382135</v>
       </c>
       <c r="CZ136" s="17">
-        <v>6.1136303834476751</v>
+        <v>5.7227699040354203</v>
       </c>
       <c r="DA136" s="17">
-        <v>7.6636284121310405</v>
+        <v>7.322404706848487</v>
       </c>
       <c r="DB136" s="7"/>
       <c r="DC136" s="7"/>
@@ -25175,31 +25177,31 @@
         <v>0.12491828913355107</v>
       </c>
       <c r="CS137" s="17">
-        <v>0.12988283602635822</v>
+        <v>0.12988283602635817</v>
       </c>
       <c r="CT137" s="17">
-        <v>5.6823615723034841E-2</v>
+        <v>5.6960321063491179E-2</v>
       </c>
       <c r="CU137" s="17">
-        <v>5.3559809402172226E-2</v>
+        <v>5.3807501106509725E-2</v>
       </c>
       <c r="CV137" s="17">
-        <v>0.12505270460479367</v>
+        <v>0.12552787919851205</v>
       </c>
       <c r="CW137" s="17">
-        <v>0.10564124100200911</v>
+        <v>0.10612055158049839</v>
       </c>
       <c r="CX137" s="17">
-        <v>5.9723612513942856E-2</v>
+        <v>5.8581691163754883E-2</v>
       </c>
       <c r="CY137" s="17">
-        <v>6.1786598631622856E-2</v>
+        <v>6.3487285916178637E-2</v>
       </c>
       <c r="CZ137" s="17">
-        <v>0.13626121376742384</v>
+        <v>0.13904470301097246</v>
       </c>
       <c r="DA137" s="17">
-        <v>0.11455855862395145</v>
+        <v>0.12786826083711939</v>
       </c>
       <c r="DB137" s="7"/>
       <c r="DC137" s="7"/>
@@ -25566,31 +25568,31 @@
         <v>23.587183405137573</v>
       </c>
       <c r="CS138" s="17">
-        <v>15.034562257530714</v>
+        <v>15.034562257530709</v>
       </c>
       <c r="CT138" s="17">
-        <v>15.592722478093865</v>
+        <v>15.620230740667632</v>
       </c>
       <c r="CU138" s="17">
-        <v>18.174129446797359</v>
+        <v>18.237037896206218</v>
       </c>
       <c r="CV138" s="17">
-        <v>19.460924397105529</v>
+        <v>19.534871912859014</v>
       </c>
       <c r="CW138" s="17">
-        <v>12.952949715762976</v>
+        <v>12.99542752650679</v>
       </c>
       <c r="CX138" s="17">
-        <v>15.291634555791624</v>
+        <v>15.390921568381852</v>
       </c>
       <c r="CY138" s="17">
-        <v>15.379173378036469</v>
+        <v>15.510167200573116</v>
       </c>
       <c r="CZ138" s="17">
-        <v>17.519790568720499</v>
+        <v>17.652076937543139</v>
       </c>
       <c r="DA138" s="17">
-        <v>11.205966671569282</v>
+        <v>11.306568476522756</v>
       </c>
       <c r="DB138" s="7"/>
       <c r="DC138" s="7"/>
@@ -25957,31 +25959,31 @@
         <v>0.71653933649787294</v>
       </c>
       <c r="CS139" s="17">
-        <v>0.76869199494990825</v>
+        <v>0.76869199494990792</v>
       </c>
       <c r="CT139" s="17">
-        <v>0.51709740797132919</v>
+        <v>0.5180096573424493</v>
       </c>
       <c r="CU139" s="17">
-        <v>0.59532109502435526</v>
+        <v>0.59738175642208546</v>
       </c>
       <c r="CV139" s="17">
-        <v>0.75990542666338379</v>
+        <v>0.76279291121256099</v>
       </c>
       <c r="CW139" s="17">
-        <v>0.70852515017306528</v>
+        <v>0.71084868248784439</v>
       </c>
       <c r="CX139" s="17">
-        <v>0.53046754715017719</v>
+        <v>0.53391181845030833</v>
       </c>
       <c r="CY139" s="17">
-        <v>0.64307502270765871</v>
+        <v>0.64855248585419034</v>
       </c>
       <c r="CZ139" s="17">
-        <v>0.79866298360606136</v>
+        <v>0.8046934338902636</v>
       </c>
       <c r="DA139" s="17">
-        <v>0.75942528608864324</v>
+        <v>0.76624304280227507</v>
       </c>
       <c r="DB139" s="7"/>
       <c r="DC139" s="7"/>
@@ -26348,31 +26350,31 @@
         <v>12.272296019097633</v>
       </c>
       <c r="CS140" s="17">
-        <v>14.125841295690492</v>
+        <v>14.125841295690526</v>
       </c>
       <c r="CT140" s="17">
-        <v>14.973149298688861</v>
+        <v>14.999564526885429</v>
       </c>
       <c r="CU140" s="17">
-        <v>15.266334306707421</v>
+        <v>15.319177631181566</v>
       </c>
       <c r="CV140" s="17">
-        <v>13.459622399941296</v>
+        <v>13.510766200674812</v>
       </c>
       <c r="CW140" s="17">
-        <v>15.649065484807757</v>
+        <v>15.700384918339742</v>
       </c>
       <c r="CX140" s="17">
-        <v>16.671794677616273</v>
+        <v>16.780042928123358</v>
       </c>
       <c r="CY140" s="17">
-        <v>16.110803039782169</v>
+        <v>16.248028599468622</v>
       </c>
       <c r="CZ140" s="17">
-        <v>13.954793659257774</v>
+        <v>14.060161869774419</v>
       </c>
       <c r="DA140" s="17">
-        <v>15.960767070606579</v>
+        <v>15.966634173610309</v>
       </c>
       <c r="DB140" s="7"/>
       <c r="DC140" s="7"/>
@@ -26739,31 +26741,31 @@
         <v>45.716634485425956</v>
       </c>
       <c r="CS141" s="17">
-        <v>50.164784452801726</v>
+        <v>50.164784452801705</v>
       </c>
       <c r="CT141" s="17">
-        <v>50.193378728564909</v>
+        <v>50.281928540406284</v>
       </c>
       <c r="CU141" s="17">
-        <v>50.6958600069757</v>
+        <v>50.871340101019456</v>
       </c>
       <c r="CV141" s="17">
-        <v>49.559654218661379</v>
+        <v>49.747970725950047</v>
       </c>
       <c r="CW141" s="17">
-        <v>52.703703513419327</v>
+        <v>52.877506933919982</v>
       </c>
       <c r="CX141" s="17">
-        <v>47.88378956091568</v>
+        <v>48.273908061917908</v>
       </c>
       <c r="CY141" s="17">
-        <v>52.99292728071773</v>
+        <v>53.267508961217004</v>
       </c>
       <c r="CZ141" s="17">
-        <v>51.308939365078267</v>
+        <v>51.698498385235482</v>
       </c>
       <c r="DA141" s="17">
-        <v>53.659980188928635</v>
+        <v>53.6842050460303</v>
       </c>
       <c r="DB141" s="7"/>
       <c r="DC141" s="7"/>
@@ -27130,31 +27132,31 @@
         <v>9.3248307421026109</v>
       </c>
       <c r="CS142" s="17">
-        <v>9.3769369130954239</v>
+        <v>9.3769369130954203</v>
       </c>
       <c r="CT142" s="17">
-        <v>7.1111627047325445</v>
+        <v>7.1421221418637257</v>
       </c>
       <c r="CU142" s="17">
-        <v>9.2352203333657865</v>
+        <v>9.2941869202721588</v>
       </c>
       <c r="CV142" s="17">
-        <v>9.0364705668052814</v>
+        <v>9.0839113699532952</v>
       </c>
       <c r="CW142" s="17">
-        <v>8.6094972662829452</v>
+        <v>8.598802621738459</v>
       </c>
       <c r="CX142" s="17">
-        <v>7.3461365874821913</v>
+        <v>7.6072302937465421</v>
       </c>
       <c r="CY142" s="17">
-        <v>8.6002913586095815</v>
+        <v>8.4534730672584146</v>
       </c>
       <c r="CZ142" s="17">
-        <v>8.4997080047049138</v>
+        <v>8.4025392329345259</v>
       </c>
       <c r="DA142" s="17">
-        <v>8.4376805747191224</v>
+        <v>8.7059844182584953</v>
       </c>
       <c r="DB142" s="7"/>
       <c r="DC142" s="7"/>
@@ -27521,31 +27523,31 @@
         <v>1.2098708265997535</v>
       </c>
       <c r="CS143" s="17">
-        <v>1.7736464643125665</v>
+        <v>1.7736464643125658</v>
       </c>
       <c r="CT143" s="17">
-        <v>0.99573000937301348</v>
+        <v>0.9681282551303958</v>
       </c>
       <c r="CU143" s="17">
-        <v>1.8639985783414117</v>
+        <v>1.6537937841458974</v>
       </c>
       <c r="CV143" s="17">
-        <v>1.4549347039072194</v>
+        <v>1.4377584485571593</v>
       </c>
       <c r="CW143" s="17">
-        <v>1.9541048547828466</v>
+        <v>1.8582739663886998</v>
       </c>
       <c r="CX143" s="17">
-        <v>1.3928483080887573</v>
+        <v>1.1195993862373728</v>
       </c>
       <c r="CY143" s="17">
-        <v>1.8533210580830541</v>
+        <v>1.6737141626742791</v>
       </c>
       <c r="CZ143" s="17">
-        <v>1.6682138214173834</v>
+        <v>1.5202155335757732</v>
       </c>
       <c r="DA143" s="17">
-        <v>2.1979932373327373</v>
+        <v>2.1200918750902518</v>
       </c>
       <c r="DB143" s="7"/>
       <c r="DC143" s="7"/>
@@ -28677,7 +28679,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28687,7 +28689,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -29465,28 +29467,28 @@
         <v>7.5394077386704534</v>
       </c>
       <c r="CT161" s="17">
-        <v>9.1319177480754448</v>
+        <v>9.0028846126606084</v>
       </c>
       <c r="CU161" s="17">
-        <v>3.494076476497042</v>
+        <v>3.3723984810802041</v>
       </c>
       <c r="CV161" s="17">
-        <v>5.7137482471742729</v>
+        <v>5.3896246183259633</v>
       </c>
       <c r="CW161" s="17">
-        <v>6.5397675145689407</v>
+        <v>6.3919733158411045</v>
       </c>
       <c r="CX161" s="17">
-        <v>9.2827126583372728</v>
+        <v>8.7704664039919216</v>
       </c>
       <c r="CY161" s="17">
-        <v>3.7419991164418964</v>
+        <v>3.5484172123765498</v>
       </c>
       <c r="CZ161" s="17">
-        <v>5.7888701256692352</v>
+        <v>5.417329460069924</v>
       </c>
       <c r="DA161" s="17">
-        <v>6.9026078180902779</v>
+        <v>6.5936864929482306</v>
       </c>
       <c r="DB161" s="7"/>
       <c r="DC161" s="7"/>
@@ -29856,28 +29858,28 @@
         <v>0.1312180955280251</v>
       </c>
       <c r="CT162" s="17">
-        <v>5.5946479456308616E-2</v>
+        <v>5.6068520889536629E-2</v>
       </c>
       <c r="CU162" s="17">
-        <v>5.2674226130687132E-2</v>
+        <v>5.2904248960629625E-2</v>
       </c>
       <c r="CV162" s="17">
-        <v>0.12273684070358128</v>
+        <v>0.12317210948768298</v>
       </c>
       <c r="CW162" s="17">
-        <v>0.10553107581446929</v>
+        <v>0.10598809766643986</v>
       </c>
       <c r="CX162" s="17">
-        <v>5.8744084636155727E-2</v>
+        <v>5.7567547433711917E-2</v>
       </c>
       <c r="CY162" s="17">
-        <v>6.0575832555719793E-2</v>
+        <v>6.2214184686531254E-2</v>
       </c>
       <c r="CZ162" s="17">
-        <v>0.13325674340085383</v>
+        <v>0.1359426487421663</v>
       </c>
       <c r="DA162" s="17">
-        <v>0.11391212890822985</v>
+        <v>0.12711622630167224</v>
       </c>
       <c r="DB162" s="7"/>
       <c r="DC162" s="7"/>
@@ -30247,28 +30249,28 @@
         <v>14.657441360079027</v>
       </c>
       <c r="CT163" s="17">
-        <v>14.898325808857143</v>
+        <v>14.921268172809171</v>
       </c>
       <c r="CU163" s="17">
-        <v>17.252061983313645</v>
+        <v>17.307338290580187</v>
       </c>
       <c r="CV163" s="17">
-        <v>18.668905316102226</v>
+        <v>18.735111938913011</v>
       </c>
       <c r="CW163" s="17">
-        <v>12.672271603334842</v>
+        <v>12.711215805689477</v>
       </c>
       <c r="CX163" s="17">
-        <v>14.508099818347345</v>
+        <v>14.588780839656318</v>
       </c>
       <c r="CY163" s="17">
-        <v>14.599030569740517</v>
+        <v>14.716517570484299</v>
       </c>
       <c r="CZ163" s="17">
-        <v>16.831221884063531</v>
+        <v>16.953793263976944</v>
       </c>
       <c r="DA163" s="17">
-        <v>10.97429360742241</v>
+        <v>11.070159325943713</v>
       </c>
       <c r="DB163" s="7"/>
       <c r="DC163" s="7"/>
@@ -30638,28 +30640,28 @@
         <v>0.75991613340255604</v>
       </c>
       <c r="CT164" s="17">
-        <v>0.51948204912399176</v>
+        <v>0.52028201459598222</v>
       </c>
       <c r="CU164" s="17">
-        <v>0.60226558528518337</v>
+        <v>0.60419526868073858</v>
       </c>
       <c r="CV164" s="17">
-        <v>0.76039786422811106</v>
+        <v>0.76309450732156847</v>
       </c>
       <c r="CW164" s="17">
-        <v>0.69695331906558555</v>
+        <v>0.69909518375559743</v>
       </c>
       <c r="CX164" s="17">
-        <v>0.53413933307097561</v>
+        <v>0.53710973632522951</v>
       </c>
       <c r="CY164" s="17">
-        <v>0.64539002187909467</v>
+        <v>0.65058385564896848</v>
       </c>
       <c r="CZ164" s="17">
-        <v>0.79184191160931983</v>
+        <v>0.79760840654639431</v>
       </c>
       <c r="DA164" s="17">
-        <v>0.7373492248418424</v>
+        <v>0.7437903239931154</v>
       </c>
       <c r="DB164" s="7"/>
       <c r="DC164" s="7"/>
@@ -31029,28 +31031,28 @@
         <v>16.217031343757483</v>
       </c>
       <c r="CT165" s="17">
-        <v>17.42840676124252</v>
+        <v>17.455245270223354</v>
       </c>
       <c r="CU165" s="17">
-        <v>17.624318220229615</v>
+        <v>17.680787251597984</v>
       </c>
       <c r="CV165" s="17">
-        <v>15.780712150856143</v>
+        <v>15.836676206560906</v>
       </c>
       <c r="CW165" s="17">
-        <v>18.051693259888381</v>
+        <v>18.107169406325447</v>
       </c>
       <c r="CX165" s="17">
-        <v>19.389052634483527</v>
+        <v>19.496877131719565</v>
       </c>
       <c r="CY165" s="17">
-        <v>18.541328880780757</v>
+        <v>18.690541878835717</v>
       </c>
       <c r="CZ165" s="17">
-        <v>16.302425803220466</v>
+        <v>16.421146288304723</v>
       </c>
       <c r="DA165" s="17">
-        <v>18.608852937349486</v>
+        <v>18.611227781166669</v>
       </c>
       <c r="DB165" s="7"/>
       <c r="DC165" s="7"/>
@@ -31420,28 +31422,28 @@
         <v>49.579343128251104</v>
       </c>
       <c r="CT166" s="17">
-        <v>50.05418678236915</v>
+        <v>50.13126667612481</v>
       </c>
       <c r="CU166" s="17">
-        <v>50.04197851358623</v>
+        <v>50.202315045139279</v>
       </c>
       <c r="CV166" s="17">
-        <v>48.693647357622218</v>
+        <v>48.866332466325773</v>
       </c>
       <c r="CW166" s="17">
-        <v>51.516568658966257</v>
+        <v>51.675830260426579</v>
       </c>
       <c r="CX166" s="17">
-        <v>47.704694717734753</v>
+        <v>48.048807328555121</v>
       </c>
       <c r="CY166" s="17">
-        <v>52.146582361020279</v>
+        <v>52.392349750721138</v>
       </c>
       <c r="CZ166" s="17">
-        <v>50.233664443994329</v>
+        <v>50.601590721064483</v>
       </c>
       <c r="DA166" s="17">
-        <v>52.209779465379967</v>
+        <v>52.218720647677173</v>
       </c>
       <c r="DB166" s="7"/>
       <c r="DC166" s="7"/>
@@ -31811,28 +31813,28 @@
         <v>9.3214362198973895</v>
       </c>
       <c r="CT167" s="17">
-        <v>6.927194214584925</v>
+        <v>6.9557953210342767</v>
       </c>
       <c r="CU167" s="17">
-        <v>9.0896419030947015</v>
+        <v>9.1453325965546846</v>
       </c>
       <c r="CV167" s="17">
-        <v>8.7864279167954145</v>
+        <v>8.8303259955166347</v>
       </c>
       <c r="CW167" s="17">
-        <v>8.4626140480659284</v>
+        <v>8.4503646460493496</v>
       </c>
       <c r="CX167" s="17">
-        <v>7.1490761163458361</v>
+        <v>7.3963122358307016</v>
       </c>
       <c r="CY167" s="17">
-        <v>8.4383714773417378</v>
+        <v>8.2904517836974865</v>
       </c>
       <c r="CZ167" s="17">
-        <v>8.2347915399060216</v>
+        <v>8.1384835237283433</v>
       </c>
       <c r="DA167" s="17">
-        <v>8.2555379668430682</v>
+        <v>8.51600660754983</v>
       </c>
       <c r="DB167" s="7"/>
       <c r="DC167" s="7"/>
@@ -32202,28 +32204,28 @@
         <v>1.7942059804139585</v>
       </c>
       <c r="CT168" s="17">
-        <v>0.98454015629051617</v>
+        <v>0.95718941166226945</v>
       </c>
       <c r="CU168" s="17">
-        <v>1.8429830918629142</v>
+        <v>1.6347288174062935</v>
       </c>
       <c r="CV168" s="17">
-        <v>1.4734243065180304</v>
+        <v>1.4556621575484705</v>
       </c>
       <c r="CW168" s="17">
-        <v>1.9546005202955881</v>
+        <v>1.8583632842460185</v>
       </c>
       <c r="CX168" s="17">
-        <v>1.3734806370441359</v>
+        <v>1.1040787764874334</v>
       </c>
       <c r="CY168" s="17">
-        <v>1.826721740239992</v>
+        <v>1.6489237635493001</v>
       </c>
       <c r="CZ168" s="17">
-        <v>1.6839275481362517</v>
+        <v>1.5341056875670138</v>
       </c>
       <c r="DA168" s="17">
-        <v>2.1976668511647297</v>
+        <v>2.1192925944195911</v>
       </c>
       <c r="DB168" s="7"/>
       <c r="DC168" s="7"/>

--- a/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E94C25-F818-436C-9BBB-06282A2E6B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CBC910-A869-44AD-A720-BC3ADFD35401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="EOS" sheetId="5" r:id="rId1"/>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">EOS!$A$1:$DA$173</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">EOS!$A$1:$DB$173</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -703,10 +703,13 @@
     <t>Table 7.2.7 Exports of Services</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1222,8 +1225,8 @@
   <cols>
     <col min="1" max="1" width="56.28515625" style="1" customWidth="1"/>
     <col min="2" max="93" width="12.85546875" style="1" customWidth="1"/>
-    <col min="94" max="105" width="12.85546875" style="18" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="1"/>
+    <col min="94" max="106" width="12.85546875" style="18" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1238,7 +1241,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1248,7 +1251,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1414,6 +1417,9 @@
       <c r="CY9" s="19"/>
       <c r="CZ9" s="19"/>
       <c r="DA9" s="19"/>
+      <c r="DB9" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -1728,6 +1734,9 @@
       </c>
       <c r="DA10" s="20" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="20" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2049,7 +2058,9 @@
       <c r="DA12" s="15">
         <v>61885.180174758614</v>
       </c>
-      <c r="DB12" s="7"/>
+      <c r="DB12" s="15">
+        <v>113902.69796741771</v>
+      </c>
       <c r="DC12" s="7"/>
       <c r="DD12" s="7"/>
       <c r="DE12" s="7"/>
@@ -2440,7 +2451,9 @@
       <c r="DA13" s="15">
         <v>1080.6764549816762</v>
       </c>
-      <c r="DB13" s="7"/>
+      <c r="DB13" s="15">
+        <v>691.21310643010111</v>
+      </c>
       <c r="DC13" s="7"/>
       <c r="DD13" s="7"/>
       <c r="DE13" s="7"/>
@@ -2831,7 +2844,9 @@
       <c r="DA14" s="15">
         <v>95557.27323749724</v>
       </c>
-      <c r="DB14" s="7"/>
+      <c r="DB14" s="15">
+        <v>164560.33349569319</v>
+      </c>
       <c r="DC14" s="7"/>
       <c r="DD14" s="7"/>
       <c r="DE14" s="7"/>
@@ -3222,7 +3237,9 @@
       <c r="DA15" s="15">
         <v>6475.8901836064888</v>
       </c>
-      <c r="DB15" s="7"/>
+      <c r="DB15" s="15">
+        <v>5751.987236458689</v>
+      </c>
       <c r="DC15" s="7"/>
       <c r="DD15" s="7"/>
       <c r="DE15" s="7"/>
@@ -3613,7 +3630,9 @@
       <c r="DA16" s="15">
         <v>134941.74006719203</v>
       </c>
-      <c r="DB16" s="7"/>
+      <c r="DB16" s="15">
+        <v>185701.12732818825</v>
+      </c>
       <c r="DC16" s="7"/>
       <c r="DD16" s="7"/>
       <c r="DE16" s="7"/>
@@ -4004,7 +4023,9 @@
       <c r="DA17" s="15">
         <v>453711.15566789632</v>
       </c>
-      <c r="DB17" s="7"/>
+      <c r="DB17" s="15">
+        <v>533298.22377584793</v>
+      </c>
       <c r="DC17" s="7"/>
       <c r="DD17" s="7"/>
       <c r="DE17" s="7"/>
@@ -4395,7 +4416,9 @@
       <c r="DA18" s="15">
         <v>73578.480825932318</v>
       </c>
-      <c r="DB18" s="7"/>
+      <c r="DB18" s="15">
+        <v>85883.023619640415</v>
+      </c>
       <c r="DC18" s="7"/>
       <c r="DD18" s="7"/>
       <c r="DE18" s="7"/>
@@ -4786,7 +4809,9 @@
       <c r="DA19" s="15">
         <v>17917.920810125586</v>
       </c>
-      <c r="DB19" s="7"/>
+      <c r="DB19" s="15">
+        <v>13314.121046315191</v>
+      </c>
       <c r="DC19" s="7"/>
       <c r="DD19" s="7"/>
       <c r="DE19" s="7"/>
@@ -4966,7 +4991,7 @@
       <c r="CY20" s="21"/>
       <c r="CZ20" s="21"/>
       <c r="DA20" s="21"/>
-      <c r="DB20" s="7"/>
+      <c r="DB20" s="21"/>
       <c r="DC20" s="7"/>
       <c r="DD20" s="7"/>
       <c r="DE20" s="7"/>
@@ -5357,7 +5382,9 @@
       <c r="DA21" s="14">
         <v>845148.31742199033</v>
       </c>
-      <c r="DB21" s="7"/>
+      <c r="DB21" s="14">
+        <v>1103102.7275759915</v>
+      </c>
       <c r="DC21" s="7"/>
       <c r="DD21" s="7"/>
       <c r="DE21" s="7"/>
@@ -5538,6 +5565,7 @@
       <c r="CY22" s="22"/>
       <c r="CZ22" s="22"/>
       <c r="DA22" s="22"/>
+      <c r="DB22" s="22"/>
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
@@ -5649,7 +5677,7 @@
       <c r="CY24" s="21"/>
       <c r="CZ24" s="21"/>
       <c r="DA24" s="21"/>
-      <c r="DB24" s="7"/>
+      <c r="DB24" s="21"/>
       <c r="DC24" s="7"/>
       <c r="DD24" s="7"/>
       <c r="DE24" s="7"/>
@@ -5829,7 +5857,7 @@
       <c r="CY25" s="21"/>
       <c r="CZ25" s="21"/>
       <c r="DA25" s="21"/>
-      <c r="DB25" s="7"/>
+      <c r="DB25" s="21"/>
       <c r="DC25" s="7"/>
       <c r="DD25" s="7"/>
       <c r="DE25" s="7"/>
@@ -5916,7 +5944,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5926,7 +5954,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6092,6 +6120,9 @@
       <c r="CY34" s="19"/>
       <c r="CZ34" s="19"/>
       <c r="DA34" s="19"/>
+      <c r="DB34" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -6406,6 +6437,9 @@
       </c>
       <c r="DA35" s="16" t="s">
         <v>5</v>
+      </c>
+      <c r="DB35" s="16" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6727,7 +6761,9 @@
       <c r="DA37" s="15">
         <v>45575.060517017955</v>
       </c>
-      <c r="DB37" s="7"/>
+      <c r="DB37" s="15">
+        <v>77398.912649426013</v>
+      </c>
       <c r="DC37" s="7"/>
       <c r="DD37" s="7"/>
       <c r="DE37" s="7"/>
@@ -7118,7 +7154,9 @@
       <c r="DA38" s="15">
         <v>878.61770689120135</v>
       </c>
-      <c r="DB38" s="7"/>
+      <c r="DB38" s="15">
+        <v>537.01507590044059</v>
+      </c>
       <c r="DC38" s="7"/>
       <c r="DD38" s="7"/>
       <c r="DE38" s="7"/>
@@ -7509,7 +7547,9 @@
       <c r="DA39" s="15">
         <v>76516.100932686037</v>
       </c>
-      <c r="DB39" s="7"/>
+      <c r="DB39" s="15">
+        <v>124198.89298361511</v>
+      </c>
       <c r="DC39" s="7"/>
       <c r="DD39" s="7"/>
       <c r="DE39" s="7"/>
@@ -7900,7 +7940,9 @@
       <c r="DA40" s="15">
         <v>5141.0222588246997</v>
       </c>
-      <c r="DB40" s="7"/>
+      <c r="DB40" s="15">
+        <v>4592.334449583479</v>
+      </c>
       <c r="DC40" s="7"/>
       <c r="DD40" s="7"/>
       <c r="DE40" s="7"/>
@@ -8291,7 +8333,9 @@
       <c r="DA41" s="15">
         <v>128639.39365782891</v>
       </c>
-      <c r="DB41" s="7"/>
+      <c r="DB41" s="15">
+        <v>175017.23262985493</v>
+      </c>
       <c r="DC41" s="7"/>
       <c r="DD41" s="7"/>
       <c r="DE41" s="7"/>
@@ -8682,7 +8726,9 @@
       <c r="DA42" s="15">
         <v>360931.83322930959</v>
       </c>
-      <c r="DB42" s="7"/>
+      <c r="DB42" s="15">
+        <v>419661.35771909857</v>
+      </c>
       <c r="DC42" s="7"/>
       <c r="DD42" s="7"/>
       <c r="DE42" s="7"/>
@@ -9073,7 +9119,9 @@
       <c r="DA43" s="15">
         <v>58861.991227136663</v>
       </c>
-      <c r="DB43" s="7"/>
+      <c r="DB43" s="15">
+        <v>66016.833538281644</v>
+      </c>
       <c r="DC43" s="7"/>
       <c r="DD43" s="7"/>
       <c r="DE43" s="7"/>
@@ -9464,7 +9512,9 @@
       <c r="DA44" s="15">
         <v>14648.389538574198</v>
       </c>
-      <c r="DB44" s="7"/>
+      <c r="DB44" s="15">
+        <v>10374.460937365184</v>
+      </c>
       <c r="DC44" s="7"/>
       <c r="DD44" s="7"/>
       <c r="DE44" s="7"/>
@@ -9644,7 +9694,7 @@
       <c r="CY45" s="21"/>
       <c r="CZ45" s="21"/>
       <c r="DA45" s="21"/>
-      <c r="DB45" s="7"/>
+      <c r="DB45" s="21"/>
       <c r="DC45" s="7"/>
       <c r="DD45" s="7"/>
       <c r="DE45" s="7"/>
@@ -10035,7 +10085,9 @@
       <c r="DA46" s="14">
         <v>691192.40906826931</v>
       </c>
-      <c r="DB46" s="7"/>
+      <c r="DB46" s="14">
+        <v>877797.03998312529</v>
+      </c>
       <c r="DC46" s="7"/>
       <c r="DD46" s="7"/>
       <c r="DE46" s="7"/>
@@ -10216,6 +10268,7 @@
       <c r="CY47" s="22"/>
       <c r="CZ47" s="22"/>
       <c r="DA47" s="22"/>
+      <c r="DB47" s="22"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
@@ -10327,7 +10380,7 @@
       <c r="CY49" s="21"/>
       <c r="CZ49" s="21"/>
       <c r="DA49" s="21"/>
-      <c r="DB49" s="7"/>
+      <c r="DB49" s="21"/>
       <c r="DC49" s="7"/>
       <c r="DD49" s="7"/>
       <c r="DE49" s="7"/>
@@ -10507,7 +10560,7 @@
       <c r="CY50" s="21"/>
       <c r="CZ50" s="21"/>
       <c r="DA50" s="21"/>
-      <c r="DB50" s="7"/>
+      <c r="DB50" s="21"/>
       <c r="DC50" s="7"/>
       <c r="DD50" s="7"/>
       <c r="DE50" s="7"/>
@@ -10594,7 +10647,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:179" x14ac:dyDescent="0.2">
@@ -10613,10 +10666,11 @@
       <c r="CY55" s="23"/>
       <c r="CZ55" s="23"/>
       <c r="DA55" s="23"/>
+      <c r="DB55" s="23"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CS56" s="23"/>
       <c r="CW56" s="23"/>
@@ -10629,12 +10683,13 @@
       <c r="CY57" s="24"/>
       <c r="CZ57" s="24"/>
       <c r="DA57" s="24"/>
+      <c r="DB57" s="24"/>
     </row>
     <row r="58" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX58" s="24"/>
       <c r="CY58" s="24"/>
       <c r="CZ58" s="24"/>
       <c r="DA58" s="24"/>
+      <c r="DB58" s="24"/>
     </row>
     <row r="59" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -10788,10 +10843,13 @@
       <c r="CU59" s="19"/>
       <c r="CV59" s="19"/>
       <c r="CW59" s="19"/>
-      <c r="CX59" s="25"/>
+      <c r="CX59" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="CY59" s="25"/>
       <c r="CZ59" s="25"/>
       <c r="DA59" s="25"/>
+      <c r="DB59" s="25"/>
     </row>
     <row r="60" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
@@ -11095,17 +11153,20 @@
       <c r="CW60" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="CX60" s="26"/>
+      <c r="CX60" s="16" t="s">
+        <v>2</v>
+      </c>
       <c r="CY60" s="26"/>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
+      <c r="DB60" s="26"/>
     </row>
     <row r="61" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="CX61" s="24"/>
       <c r="CY61" s="24"/>
       <c r="CZ61" s="24"/>
       <c r="DA61" s="24"/>
+      <c r="DB61" s="24"/>
     </row>
     <row r="62" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
@@ -11411,11 +11472,13 @@
       <c r="CW62" s="27">
         <v>6.2109298478013812</v>
       </c>
-      <c r="CX62" s="28"/>
+      <c r="CX62" s="27">
+        <v>6.7616953389733112</v>
+      </c>
       <c r="CY62" s="28"/>
       <c r="CZ62" s="28"/>
       <c r="DA62" s="28"/>
-      <c r="DB62" s="7"/>
+      <c r="DB62" s="28"/>
       <c r="DC62" s="7"/>
       <c r="DD62" s="7"/>
       <c r="DE62" s="7"/>
@@ -11790,11 +11853,13 @@
       <c r="CW63" s="27">
         <v>25.010011005945444</v>
       </c>
-      <c r="CX63" s="28"/>
+      <c r="CX63" s="27">
+        <v>13.201838917001041</v>
+      </c>
       <c r="CY63" s="28"/>
       <c r="CZ63" s="28"/>
       <c r="DA63" s="28"/>
-      <c r="DB63" s="7"/>
+      <c r="DB63" s="28"/>
       <c r="DC63" s="7"/>
       <c r="DD63" s="7"/>
       <c r="DE63" s="7"/>
@@ -12169,11 +12234,13 @@
       <c r="CW64" s="27">
         <v>-9.7345026297581398</v>
       </c>
-      <c r="CX64" s="28"/>
+      <c r="CX64" s="27">
+        <v>2.5802979482211015</v>
+      </c>
       <c r="CY64" s="28"/>
       <c r="CZ64" s="28"/>
       <c r="DA64" s="28"/>
-      <c r="DB64" s="7"/>
+      <c r="DB64" s="28"/>
       <c r="DC64" s="7"/>
       <c r="DD64" s="7"/>
       <c r="DE64" s="7"/>
@@ -12548,11 +12615,13 @@
       <c r="CW65" s="27">
         <v>11.833242040996225</v>
       </c>
-      <c r="CX65" s="28"/>
+      <c r="CX65" s="27">
+        <v>3.3598336594911729</v>
+      </c>
       <c r="CY65" s="28"/>
       <c r="CZ65" s="28"/>
       <c r="DA65" s="28"/>
-      <c r="DB65" s="7"/>
+      <c r="DB65" s="28"/>
       <c r="DC65" s="7"/>
       <c r="DD65" s="7"/>
       <c r="DE65" s="7"/>
@@ -12927,11 +12996,13 @@
       <c r="CW66" s="27">
         <v>5.5078100348982133</v>
       </c>
-      <c r="CX66" s="28"/>
+      <c r="CX66" s="27">
+        <v>6.1756418428943221</v>
+      </c>
       <c r="CY66" s="28"/>
       <c r="CZ66" s="28"/>
       <c r="DA66" s="28"/>
-      <c r="DB66" s="7"/>
+      <c r="DB66" s="28"/>
       <c r="DC66" s="7"/>
       <c r="DD66" s="7"/>
       <c r="DE66" s="7"/>
@@ -13306,11 +13377,13 @@
       <c r="CW67" s="27">
         <v>5.3312139218381986</v>
       </c>
-      <c r="CX67" s="28"/>
+      <c r="CX67" s="27">
+        <v>5.9890746699372528</v>
+      </c>
       <c r="CY67" s="28"/>
       <c r="CZ67" s="28"/>
       <c r="DA67" s="28"/>
-      <c r="DB67" s="7"/>
+      <c r="DB67" s="28"/>
       <c r="DC67" s="7"/>
       <c r="DD67" s="7"/>
       <c r="DE67" s="7"/>
@@ -13685,11 +13758,13 @@
       <c r="CW68" s="27">
         <v>5.0416267907386469</v>
       </c>
-      <c r="CX68" s="28"/>
+      <c r="CX68" s="27">
+        <v>8.3138977321431895</v>
+      </c>
       <c r="CY68" s="28"/>
       <c r="CZ68" s="28"/>
       <c r="DA68" s="28"/>
-      <c r="DB68" s="7"/>
+      <c r="DB68" s="28"/>
       <c r="DC68" s="7"/>
       <c r="DD68" s="7"/>
       <c r="DE68" s="7"/>
@@ -14064,11 +14139,13 @@
       <c r="CW69" s="27">
         <v>18.365864065054225</v>
       </c>
-      <c r="CX69" s="28"/>
+      <c r="CX69" s="27">
+        <v>14.091495197807831</v>
+      </c>
       <c r="CY69" s="28"/>
       <c r="CZ69" s="28"/>
       <c r="DA69" s="28"/>
-      <c r="DB69" s="7"/>
+      <c r="DB69" s="28"/>
       <c r="DC69" s="7"/>
       <c r="DD69" s="7"/>
       <c r="DE69" s="7"/>
@@ -14240,11 +14317,11 @@
       <c r="CU70" s="21"/>
       <c r="CV70" s="21"/>
       <c r="CW70" s="21"/>
-      <c r="CX70" s="29"/>
+      <c r="CX70" s="21"/>
       <c r="CY70" s="29"/>
       <c r="CZ70" s="29"/>
       <c r="DA70" s="29"/>
-      <c r="DB70" s="7"/>
+      <c r="DB70" s="29"/>
       <c r="DC70" s="7"/>
       <c r="DD70" s="7"/>
       <c r="DE70" s="7"/>
@@ -14619,11 +14696,13 @@
       <c r="CW71" s="27">
         <v>3.7484300966110595</v>
       </c>
-      <c r="CX71" s="28"/>
+      <c r="CX71" s="27">
+        <v>5.8325793348113137</v>
+      </c>
       <c r="CY71" s="28"/>
       <c r="CZ71" s="28"/>
       <c r="DA71" s="28"/>
-      <c r="DB71" s="7"/>
+      <c r="DB71" s="28"/>
       <c r="DC71" s="7"/>
       <c r="DD71" s="7"/>
       <c r="DE71" s="7"/>
@@ -14796,19 +14875,20 @@
       <c r="CU72" s="22"/>
       <c r="CV72" s="22"/>
       <c r="CW72" s="22"/>
-      <c r="CX72" s="30"/>
+      <c r="CX72" s="22"/>
       <c r="CY72" s="30"/>
       <c r="CZ72" s="30"/>
       <c r="DA72" s="30"/>
+      <c r="DB72" s="30"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="CX73" s="24"/>
       <c r="CY73" s="24"/>
       <c r="CZ73" s="24"/>
       <c r="DA73" s="24"/>
+      <c r="DB73" s="24"/>
     </row>
     <row r="74" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="7"/>
@@ -14911,11 +14991,11 @@
       <c r="CU74" s="21"/>
       <c r="CV74" s="21"/>
       <c r="CW74" s="21"/>
-      <c r="CX74" s="29"/>
+      <c r="CX74" s="21"/>
       <c r="CY74" s="29"/>
       <c r="CZ74" s="29"/>
       <c r="DA74" s="29"/>
-      <c r="DB74" s="7"/>
+      <c r="DB74" s="29"/>
       <c r="DC74" s="7"/>
       <c r="DD74" s="7"/>
       <c r="DE74" s="7"/>
@@ -15087,11 +15167,11 @@
       <c r="CU75" s="21"/>
       <c r="CV75" s="21"/>
       <c r="CW75" s="21"/>
-      <c r="CX75" s="29"/>
+      <c r="CX75" s="21"/>
       <c r="CY75" s="29"/>
       <c r="CZ75" s="29"/>
       <c r="DA75" s="29"/>
-      <c r="DB75" s="7"/>
+      <c r="DB75" s="29"/>
       <c r="DC75" s="7"/>
       <c r="DD75" s="7"/>
       <c r="DE75" s="7"/>
@@ -15166,67 +15246,67 @@
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CX76" s="24"/>
       <c r="CY76" s="24"/>
       <c r="CZ76" s="24"/>
       <c r="DA76" s="24"/>
+      <c r="DB76" s="24"/>
     </row>
     <row r="77" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CX77" s="24"/>
       <c r="CY77" s="24"/>
       <c r="CZ77" s="24"/>
       <c r="DA77" s="24"/>
+      <c r="DB77" s="24"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="CX78" s="24"/>
+        <v>56</v>
+      </c>
       <c r="CY78" s="24"/>
       <c r="CZ78" s="24"/>
       <c r="DA78" s="24"/>
+      <c r="DB78" s="24"/>
     </row>
     <row r="79" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX79" s="24"/>
       <c r="CY79" s="24"/>
       <c r="CZ79" s="24"/>
       <c r="DA79" s="24"/>
+      <c r="DB79" s="24"/>
     </row>
     <row r="80" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CX80" s="24"/>
       <c r="CY80" s="24"/>
       <c r="CZ80" s="24"/>
       <c r="DA80" s="24"/>
+      <c r="DB80" s="24"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CX81" s="24"/>
+        <v>57</v>
+      </c>
       <c r="CY81" s="24"/>
       <c r="CZ81" s="24"/>
       <c r="DA81" s="24"/>
+      <c r="DB81" s="24"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CX82" s="24"/>
       <c r="CY82" s="24"/>
       <c r="CZ82" s="24"/>
       <c r="DA82" s="24"/>
+      <c r="DB82" s="24"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX83" s="24"/>
       <c r="CY83" s="24"/>
       <c r="CZ83" s="24"/>
       <c r="DA83" s="24"/>
+      <c r="DB83" s="24"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
@@ -15380,10 +15460,13 @@
       <c r="CU84" s="19"/>
       <c r="CV84" s="19"/>
       <c r="CW84" s="19"/>
-      <c r="CX84" s="25"/>
+      <c r="CX84" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="CY84" s="25"/>
       <c r="CZ84" s="25"/>
       <c r="DA84" s="25"/>
+      <c r="DB84" s="25"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
@@ -15687,17 +15770,20 @@
       <c r="CW85" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="CX85" s="30"/>
+      <c r="CX85" s="20" t="s">
+        <v>2</v>
+      </c>
       <c r="CY85" s="30"/>
       <c r="CZ85" s="30"/>
       <c r="DA85" s="30"/>
+      <c r="DB85" s="30"/>
     </row>
     <row r="86" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="CX86" s="24"/>
       <c r="CY86" s="24"/>
       <c r="CZ86" s="24"/>
       <c r="DA86" s="24"/>
+      <c r="DB86" s="24"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -16003,11 +16089,13 @@
       <c r="CW87" s="27">
         <v>5.1741738290558033</v>
       </c>
-      <c r="CX87" s="28"/>
+      <c r="CX87" s="27">
+        <v>3.5358015507279248</v>
+      </c>
       <c r="CY87" s="28"/>
       <c r="CZ87" s="28"/>
       <c r="DA87" s="28"/>
-      <c r="DB87" s="7"/>
+      <c r="DB87" s="28"/>
       <c r="DC87" s="7"/>
       <c r="DD87" s="7"/>
       <c r="DE87" s="7"/>
@@ -16382,11 +16470,13 @@
       <c r="CW88" s="27">
         <v>22.281191730130317</v>
       </c>
-      <c r="CX88" s="28"/>
+      <c r="CX88" s="27">
+        <v>9.4427835878962725</v>
+      </c>
       <c r="CY88" s="28"/>
       <c r="CZ88" s="28"/>
       <c r="DA88" s="28"/>
-      <c r="DB88" s="7"/>
+      <c r="DB88" s="28"/>
       <c r="DC88" s="7"/>
       <c r="DD88" s="7"/>
       <c r="DE88" s="7"/>
@@ -16761,11 +16851,13 @@
       <c r="CW89" s="27">
         <v>-11.206219332361727</v>
       </c>
-      <c r="CX89" s="28"/>
+      <c r="CX89" s="27">
+        <v>-0.12032865690188999</v>
+      </c>
       <c r="CY89" s="28"/>
       <c r="CZ89" s="28"/>
       <c r="DA89" s="28"/>
-      <c r="DB89" s="7"/>
+      <c r="DB89" s="28"/>
       <c r="DC89" s="7"/>
       <c r="DD89" s="7"/>
       <c r="DE89" s="7"/>
@@ -17140,11 +17232,13 @@
       <c r="CW90" s="27">
         <v>8.4750808576495587</v>
       </c>
-      <c r="CX90" s="28"/>
+      <c r="CX90" s="27">
+        <v>0.31107026315125097</v>
+      </c>
       <c r="CY90" s="28"/>
       <c r="CZ90" s="28"/>
       <c r="DA90" s="28"/>
-      <c r="DB90" s="7"/>
+      <c r="DB90" s="28"/>
       <c r="DC90" s="7"/>
       <c r="DD90" s="7"/>
       <c r="DE90" s="7"/>
@@ -17519,11 +17613,13 @@
       <c r="CW91" s="27">
         <v>4.794919426554344</v>
       </c>
-      <c r="CX91" s="28"/>
+      <c r="CX91" s="27">
+        <v>5.3159470742307775</v>
+      </c>
       <c r="CY91" s="28"/>
       <c r="CZ91" s="28"/>
       <c r="DA91" s="28"/>
-      <c r="DB91" s="7"/>
+      <c r="DB91" s="28"/>
       <c r="DC91" s="7"/>
       <c r="DD91" s="7"/>
       <c r="DE91" s="7"/>
@@ -17859,11 +17955,13 @@
       <c r="CW92" s="27">
         <v>3.0278252845553624</v>
       </c>
-      <c r="CX92" s="28"/>
+      <c r="CX92" s="27">
+        <v>2.4695311733247109</v>
+      </c>
       <c r="CY92" s="28"/>
       <c r="CZ92" s="28"/>
       <c r="DA92" s="28"/>
-      <c r="DB92" s="7"/>
+      <c r="DB92" s="28"/>
       <c r="DC92" s="7"/>
       <c r="DD92" s="7"/>
       <c r="DE92" s="7"/>
@@ -18199,11 +18297,13 @@
       <c r="CW93" s="27">
         <v>2.748693499692763</v>
       </c>
-      <c r="CX93" s="28"/>
+      <c r="CX93" s="27">
+        <v>4.717154619298114</v>
+      </c>
       <c r="CY93" s="28"/>
       <c r="CZ93" s="28"/>
       <c r="DA93" s="28"/>
-      <c r="DB93" s="7"/>
+      <c r="DB93" s="28"/>
       <c r="DC93" s="7"/>
       <c r="DD93" s="7"/>
       <c r="DE93" s="7"/>
@@ -18578,11 +18678,13 @@
       <c r="CW94" s="27">
         <v>16.272248876773233</v>
       </c>
-      <c r="CX94" s="28"/>
+      <c r="CX94" s="27">
+        <v>10.241181240563193</v>
+      </c>
       <c r="CY94" s="28"/>
       <c r="CZ94" s="28"/>
       <c r="DA94" s="28"/>
-      <c r="DB94" s="7"/>
+      <c r="DB94" s="28"/>
       <c r="DC94" s="7"/>
       <c r="DD94" s="7"/>
       <c r="DE94" s="7"/>
@@ -18754,11 +18856,11 @@
       <c r="CU95" s="21"/>
       <c r="CV95" s="21"/>
       <c r="CW95" s="21"/>
-      <c r="CX95" s="29"/>
+      <c r="CX95" s="21"/>
       <c r="CY95" s="29"/>
       <c r="CZ95" s="29"/>
       <c r="DA95" s="29"/>
-      <c r="DB95" s="7"/>
+      <c r="DB95" s="29"/>
       <c r="DC95" s="7"/>
       <c r="DD95" s="7"/>
       <c r="DE95" s="7"/>
@@ -19133,11 +19235,13 @@
       <c r="CW96" s="27">
         <v>1.9566995412859853</v>
       </c>
-      <c r="CX96" s="28"/>
+      <c r="CX96" s="27">
+        <v>2.984648708335186</v>
+      </c>
       <c r="CY96" s="28"/>
       <c r="CZ96" s="28"/>
       <c r="DA96" s="28"/>
-      <c r="DB96" s="7"/>
+      <c r="DB96" s="28"/>
       <c r="DC96" s="7"/>
       <c r="DD96" s="7"/>
       <c r="DE96" s="7"/>
@@ -19310,19 +19414,20 @@
       <c r="CU97" s="22"/>
       <c r="CV97" s="22"/>
       <c r="CW97" s="22"/>
-      <c r="CX97" s="30"/>
+      <c r="CX97" s="22"/>
       <c r="CY97" s="30"/>
       <c r="CZ97" s="30"/>
       <c r="DA97" s="30"/>
+      <c r="DB97" s="30"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A98" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="CX98" s="24"/>
       <c r="CY98" s="24"/>
       <c r="CZ98" s="24"/>
       <c r="DA98" s="24"/>
+      <c r="DB98" s="24"/>
     </row>
     <row r="99" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="7"/>
@@ -19425,11 +19530,11 @@
       <c r="CU99" s="21"/>
       <c r="CV99" s="21"/>
       <c r="CW99" s="21"/>
-      <c r="CX99" s="29"/>
+      <c r="CX99" s="21"/>
       <c r="CY99" s="29"/>
       <c r="CZ99" s="29"/>
       <c r="DA99" s="29"/>
-      <c r="DB99" s="7"/>
+      <c r="DB99" s="29"/>
       <c r="DC99" s="7"/>
       <c r="DD99" s="7"/>
       <c r="DE99" s="7"/>
@@ -19601,11 +19706,11 @@
       <c r="CU100" s="21"/>
       <c r="CV100" s="21"/>
       <c r="CW100" s="29"/>
-      <c r="CX100" s="29"/>
+      <c r="CX100" s="21"/>
       <c r="CY100" s="29"/>
       <c r="CZ100" s="29"/>
       <c r="DA100" s="29"/>
-      <c r="DB100" s="7"/>
+      <c r="DB100" s="29"/>
       <c r="DC100" s="7"/>
       <c r="DD100" s="7"/>
       <c r="DE100" s="7"/>
@@ -19683,7 +19788,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19693,7 +19798,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -19859,6 +19964,9 @@
       <c r="CY108" s="19"/>
       <c r="CZ108" s="19"/>
       <c r="DA108" s="19"/>
+      <c r="DB108" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
@@ -20173,6 +20281,9 @@
       </c>
       <c r="DA109" s="16" t="s">
         <v>5</v>
+      </c>
+      <c r="DB109" s="16" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20494,7 +20605,9 @@
       <c r="DA111" s="27">
         <v>135.78737904615701</v>
       </c>
-      <c r="DB111" s="7"/>
+      <c r="DB111" s="27">
+        <v>147.16317590058858</v>
+      </c>
       <c r="DC111" s="7"/>
       <c r="DD111" s="7"/>
       <c r="DE111" s="7"/>
@@ -20885,7 +20998,9 @@
       <c r="DA112" s="27">
         <v>122.99734531932165</v>
       </c>
-      <c r="DB112" s="7"/>
+      <c r="DB112" s="27">
+        <v>128.71391092160843</v>
+      </c>
       <c r="DC112" s="7"/>
       <c r="DD112" s="7"/>
       <c r="DE112" s="7"/>
@@ -21276,7 +21391,9 @@
       <c r="DA113" s="27">
         <v>124.88518373611642</v>
       </c>
-      <c r="DB113" s="7"/>
+      <c r="DB113" s="27">
+        <v>132.49742372293346</v>
+      </c>
       <c r="DC113" s="7"/>
       <c r="DD113" s="7"/>
       <c r="DE113" s="7"/>
@@ -21667,7 +21784,9 @@
       <c r="DA114" s="27">
         <v>125.96502908522625</v>
       </c>
-      <c r="DB114" s="7"/>
+      <c r="DB114" s="27">
+        <v>125.25192360457086</v>
+      </c>
       <c r="DC114" s="7"/>
       <c r="DD114" s="7"/>
       <c r="DE114" s="7"/>
@@ -22058,7 +22177,9 @@
       <c r="DA115" s="27">
         <v>104.89923516440609</v>
       </c>
-      <c r="DB115" s="7"/>
+      <c r="DB115" s="27">
+        <v>106.10448156321198</v>
+      </c>
       <c r="DC115" s="7"/>
       <c r="DD115" s="7"/>
       <c r="DE115" s="7"/>
@@ -22449,7 +22570,9 @@
       <c r="DA116" s="27">
         <v>125.7054972426446</v>
       </c>
-      <c r="DB116" s="7"/>
+      <c r="DB116" s="27">
+        <v>127.07822961694093</v>
+      </c>
       <c r="DC116" s="7"/>
       <c r="DD116" s="7"/>
       <c r="DE116" s="7"/>
@@ -22840,7 +22963,9 @@
       <c r="DA117" s="27">
         <v>125.00168494471697</v>
       </c>
-      <c r="DB117" s="7"/>
+      <c r="DB117" s="27">
+        <v>130.09261277252691</v>
+      </c>
       <c r="DC117" s="7"/>
       <c r="DD117" s="7"/>
       <c r="DE117" s="7"/>
@@ -23231,7 +23356,9 @@
       <c r="DA118" s="27">
         <v>122.32007322676392</v>
       </c>
-      <c r="DB118" s="7"/>
+      <c r="DB118" s="27">
+        <v>128.33554559314382</v>
+      </c>
       <c r="DC118" s="7"/>
       <c r="DD118" s="7"/>
       <c r="DE118" s="7"/>
@@ -23411,7 +23538,7 @@
       <c r="CY119" s="21"/>
       <c r="CZ119" s="21"/>
       <c r="DA119" s="21"/>
-      <c r="DB119" s="7"/>
+      <c r="DB119" s="21"/>
       <c r="DC119" s="7"/>
       <c r="DD119" s="7"/>
       <c r="DE119" s="7"/>
@@ -23802,7 +23929,9 @@
       <c r="DA120" s="27">
         <v>122.27395821103624</v>
       </c>
-      <c r="DB120" s="7"/>
+      <c r="DB120" s="27">
+        <v>125.66717331345723</v>
+      </c>
       <c r="DC120" s="7"/>
       <c r="DD120" s="7"/>
       <c r="DE120" s="7"/>
@@ -23983,6 +24112,7 @@
       <c r="CY121" s="22"/>
       <c r="CZ121" s="22"/>
       <c r="DA121" s="22"/>
+      <c r="DB121" s="22"/>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="s">
@@ -24001,7 +24131,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24011,7 +24141,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24177,6 +24307,9 @@
       <c r="CY133" s="19"/>
       <c r="CZ133" s="19"/>
       <c r="DA133" s="19"/>
+      <c r="DB133" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
@@ -24491,6 +24624,9 @@
       </c>
       <c r="DA134" s="16" t="s">
         <v>5</v>
+      </c>
+      <c r="DB134" s="16" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24812,7 +24948,9 @@
       <c r="DA136" s="17">
         <v>7.322404706848487</v>
       </c>
-      <c r="DB136" s="7"/>
+      <c r="DB136" s="17">
+        <v>10.325665517817431</v>
+      </c>
       <c r="DC136" s="7"/>
       <c r="DD136" s="7"/>
       <c r="DE136" s="7"/>
@@ -25203,7 +25341,9 @@
       <c r="DA137" s="17">
         <v>0.12786826083711939</v>
       </c>
-      <c r="DB137" s="7"/>
+      <c r="DB137" s="17">
+        <v>6.2660810199336961E-2</v>
+      </c>
       <c r="DC137" s="7"/>
       <c r="DD137" s="7"/>
       <c r="DE137" s="7"/>
@@ -25594,7 +25734,9 @@
       <c r="DA138" s="17">
         <v>11.306568476522756</v>
       </c>
-      <c r="DB138" s="7"/>
+      <c r="DB138" s="17">
+        <v>14.917951826418344</v>
+      </c>
       <c r="DC138" s="7"/>
       <c r="DD138" s="7"/>
       <c r="DE138" s="7"/>
@@ -25985,7 +26127,9 @@
       <c r="DA139" s="17">
         <v>0.76624304280227507</v>
       </c>
-      <c r="DB139" s="7"/>
+      <c r="DB139" s="17">
+        <v>0.52143713297657868</v>
+      </c>
       <c r="DC139" s="7"/>
       <c r="DD139" s="7"/>
       <c r="DE139" s="7"/>
@@ -26376,7 +26520,9 @@
       <c r="DA140" s="17">
         <v>15.966634173610309</v>
       </c>
-      <c r="DB140" s="7"/>
+      <c r="DB140" s="17">
+        <v>16.834436420645645</v>
+      </c>
       <c r="DC140" s="7"/>
       <c r="DD140" s="7"/>
       <c r="DE140" s="7"/>
@@ -26767,7 +26913,9 @@
       <c r="DA141" s="17">
         <v>53.6842050460303</v>
       </c>
-      <c r="DB141" s="7"/>
+      <c r="DB141" s="17">
+        <v>48.345291009092314</v>
+      </c>
       <c r="DC141" s="7"/>
       <c r="DD141" s="7"/>
       <c r="DE141" s="7"/>
@@ -27158,7 +27306,9 @@
       <c r="DA142" s="17">
         <v>8.7059844182584953</v>
       </c>
-      <c r="DB142" s="7"/>
+      <c r="DB142" s="17">
+        <v>7.785587096531227</v>
+      </c>
       <c r="DC142" s="7"/>
       <c r="DD142" s="7"/>
       <c r="DE142" s="7"/>
@@ -27549,7 +27699,9 @@
       <c r="DA143" s="17">
         <v>2.1200918750902518</v>
       </c>
-      <c r="DB143" s="7"/>
+      <c r="DB143" s="17">
+        <v>1.2069701863191156</v>
+      </c>
       <c r="DC143" s="7"/>
       <c r="DD143" s="7"/>
       <c r="DE143" s="7"/>
@@ -27729,7 +27881,7 @@
       <c r="CY144" s="21"/>
       <c r="CZ144" s="21"/>
       <c r="DA144" s="21"/>
-      <c r="DB144" s="7"/>
+      <c r="DB144" s="21"/>
       <c r="DC144" s="7"/>
       <c r="DD144" s="7"/>
       <c r="DE144" s="7"/>
@@ -28120,7 +28272,9 @@
       <c r="DA145" s="27">
         <v>100</v>
       </c>
-      <c r="DB145" s="7"/>
+      <c r="DB145" s="27">
+        <v>100</v>
+      </c>
       <c r="DC145" s="7"/>
       <c r="DD145" s="7"/>
       <c r="DE145" s="7"/>
@@ -28301,6 +28455,7 @@
       <c r="CY146" s="22"/>
       <c r="CZ146" s="22"/>
       <c r="DA146" s="22"/>
+      <c r="DB146" s="22"/>
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
@@ -28412,7 +28567,7 @@
       <c r="CY148" s="21"/>
       <c r="CZ148" s="21"/>
       <c r="DA148" s="21"/>
-      <c r="DB148" s="7"/>
+      <c r="DB148" s="21"/>
       <c r="DC148" s="7"/>
       <c r="DD148" s="7"/>
       <c r="DE148" s="7"/>
@@ -28592,7 +28747,7 @@
       <c r="CY149" s="21"/>
       <c r="CZ149" s="21"/>
       <c r="DA149" s="21"/>
-      <c r="DB149" s="7"/>
+      <c r="DB149" s="21"/>
       <c r="DC149" s="7"/>
       <c r="DD149" s="7"/>
       <c r="DE149" s="7"/>
@@ -28679,7 +28834,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28689,7 +28844,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -28855,6 +29010,9 @@
       <c r="CY158" s="19"/>
       <c r="CZ158" s="19"/>
       <c r="DA158" s="19"/>
+      <c r="DB158" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="159" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
@@ -29169,6 +29327,9 @@
       </c>
       <c r="DA159" s="16" t="s">
         <v>5</v>
+      </c>
+      <c r="DB159" s="16" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -29490,7 +29651,9 @@
       <c r="DA161" s="17">
         <v>6.5936864929482306</v>
       </c>
-      <c r="DB161" s="7"/>
+      <c r="DB161" s="17">
+        <v>8.8174041519795878</v>
+      </c>
       <c r="DC161" s="7"/>
       <c r="DD161" s="7"/>
       <c r="DE161" s="7"/>
@@ -29881,7 +30044,9 @@
       <c r="DA162" s="17">
         <v>0.12711622630167224</v>
       </c>
-      <c r="DB162" s="7"/>
+      <c r="DB162" s="17">
+        <v>6.1177590199069723E-2</v>
+      </c>
       <c r="DC162" s="7"/>
       <c r="DD162" s="7"/>
       <c r="DE162" s="7"/>
@@ -30272,7 +30437,9 @@
       <c r="DA163" s="17">
         <v>11.070159325943713</v>
       </c>
-      <c r="DB163" s="7"/>
+      <c r="DB163" s="17">
+        <v>14.14893048465995</v>
+      </c>
       <c r="DC163" s="7"/>
       <c r="DD163" s="7"/>
       <c r="DE163" s="7"/>
@@ -30663,7 +30830,9 @@
       <c r="DA164" s="17">
         <v>0.7437903239931154</v>
       </c>
-      <c r="DB164" s="7"/>
+      <c r="DB164" s="17">
+        <v>0.52316586185706004</v>
+      </c>
       <c r="DC164" s="7"/>
       <c r="DD164" s="7"/>
       <c r="DE164" s="7"/>
@@ -31054,7 +31223,9 @@
       <c r="DA165" s="17">
         <v>18.611227781166669</v>
       </c>
-      <c r="DB165" s="7"/>
+      <c r="DB165" s="17">
+        <v>19.938234541462961</v>
+      </c>
       <c r="DC165" s="7"/>
       <c r="DD165" s="7"/>
       <c r="DE165" s="7"/>
@@ -31445,7 +31616,9 @@
       <c r="DA166" s="17">
         <v>52.218720647677173</v>
       </c>
-      <c r="DB166" s="7"/>
+      <c r="DB166" s="17">
+        <v>47.808472642738245</v>
+      </c>
       <c r="DC166" s="7"/>
       <c r="DD166" s="7"/>
       <c r="DE166" s="7"/>
@@ -31836,7 +32009,9 @@
       <c r="DA167" s="17">
         <v>8.51600660754983</v>
       </c>
-      <c r="DB167" s="7"/>
+      <c r="DB167" s="17">
+        <v>7.5207400493798371</v>
+      </c>
       <c r="DC167" s="7"/>
       <c r="DD167" s="7"/>
       <c r="DE167" s="7"/>
@@ -32227,7 +32402,9 @@
       <c r="DA168" s="17">
         <v>2.1192925944195911</v>
       </c>
-      <c r="DB168" s="7"/>
+      <c r="DB168" s="17">
+        <v>1.1818746777232947</v>
+      </c>
       <c r="DC168" s="7"/>
       <c r="DD168" s="7"/>
       <c r="DE168" s="7"/>
@@ -32407,7 +32584,7 @@
       <c r="CY169" s="21"/>
       <c r="CZ169" s="21"/>
       <c r="DA169" s="21"/>
-      <c r="DB169" s="7"/>
+      <c r="DB169" s="21"/>
       <c r="DC169" s="7"/>
       <c r="DD169" s="7"/>
       <c r="DE169" s="7"/>
@@ -32798,7 +32975,9 @@
       <c r="DA170" s="27">
         <v>100</v>
       </c>
-      <c r="DB170" s="7"/>
+      <c r="DB170" s="27">
+        <v>100</v>
+      </c>
       <c r="DC170" s="7"/>
       <c r="DD170" s="7"/>
       <c r="DE170" s="7"/>
@@ -32979,6 +33158,7 @@
       <c r="CY171" s="22"/>
       <c r="CZ171" s="22"/>
       <c r="DA171" s="22"/>
+      <c r="DB171" s="22"/>
     </row>
     <row r="172" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A172" s="10" t="s">
@@ -33091,7 +33271,7 @@
       <c r="CY173" s="31"/>
       <c r="CZ173" s="31"/>
       <c r="DA173" s="31"/>
-      <c r="DB173" s="12"/>
+      <c r="DB173" s="31"/>
       <c r="DC173" s="12"/>
       <c r="DD173" s="12"/>
       <c r="DE173" s="12"/>
@@ -33175,6 +33355,7 @@
       <c r="CY174" s="24"/>
       <c r="CZ174" s="24"/>
       <c r="DA174" s="24"/>
+      <c r="DB174" s="24"/>
     </row>
     <row r="175" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT175" s="23"/>
@@ -33185,15 +33366,16 @@
       <c r="CY175" s="24"/>
       <c r="CZ175" s="24"/>
       <c r="DA175" s="24"/>
+      <c r="DB175" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="50" max="81" man="1"/>
-    <brk id="100" max="81" man="1"/>
-    <brk id="124" max="81" man="1"/>
+    <brk id="50" max="105" man="1"/>
+    <brk id="100" max="105" man="1"/>
+    <brk id="124" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-05EOS_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CBC910-A869-44AD-A720-BC3ADFD35401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934C2AA7-61E2-4CC5-BA8A-4A1C8149EF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">EOS!$A$1:$DB$173</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">EOS!$A$1:$DC$173</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -703,13 +703,13 @@
     <t>Table 7.2.7 Exports of Services</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1220,13 +1220,13 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:FW175"/>
+  <dimension ref="A1:FW177"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.28515625" style="1" customWidth="1"/>
     <col min="2" max="93" width="12.85546875" style="1" customWidth="1"/>
-    <col min="94" max="106" width="12.85546875" style="18" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="1"/>
+    <col min="94" max="107" width="12.85546875" style="18" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1241,7 +1241,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1420,6 +1420,7 @@
       <c r="DB9" s="19">
         <v>2026</v>
       </c>
+      <c r="DC9" s="19"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -1737,6 +1738,9 @@
       </c>
       <c r="DB10" s="20" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="20" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2059,9 +2063,11 @@
         <v>61885.180174758614</v>
       </c>
       <c r="DB12" s="15">
-        <v>113902.69796741771</v>
-      </c>
-      <c r="DC12" s="7"/>
+        <v>112276.02518138663</v>
+      </c>
+      <c r="DC12" s="15">
+        <v>35145.276680183728</v>
+      </c>
       <c r="DD12" s="7"/>
       <c r="DE12" s="7"/>
       <c r="DF12" s="7"/>
@@ -2452,9 +2458,11 @@
         <v>1080.6764549816762</v>
       </c>
       <c r="DB13" s="15">
-        <v>691.21310643010111</v>
-      </c>
-      <c r="DC13" s="7"/>
+        <v>1053.9907943137964</v>
+      </c>
+      <c r="DC13" s="15">
+        <v>615.62401999733493</v>
+      </c>
       <c r="DD13" s="7"/>
       <c r="DE13" s="7"/>
       <c r="DF13" s="7"/>
@@ -2847,7 +2855,9 @@
       <c r="DB14" s="15">
         <v>164560.33349569319</v>
       </c>
-      <c r="DC14" s="7"/>
+      <c r="DC14" s="15">
+        <v>165836.61476016074</v>
+      </c>
       <c r="DD14" s="7"/>
       <c r="DE14" s="7"/>
       <c r="DF14" s="7"/>
@@ -3238,9 +3248,11 @@
         <v>6475.8901836064888</v>
       </c>
       <c r="DB15" s="15">
-        <v>5751.987236458689</v>
-      </c>
-      <c r="DC15" s="7"/>
+        <v>5823.4764673639311</v>
+      </c>
+      <c r="DC15" s="15">
+        <v>6561.5883175077743</v>
+      </c>
       <c r="DD15" s="7"/>
       <c r="DE15" s="7"/>
       <c r="DF15" s="7"/>
@@ -3631,9 +3643,11 @@
         <v>134941.74006719203</v>
       </c>
       <c r="DB16" s="15">
-        <v>185701.12732818825</v>
-      </c>
-      <c r="DC16" s="7"/>
+        <v>182318.49200302071</v>
+      </c>
+      <c r="DC16" s="15">
+        <v>159209.37568950476</v>
+      </c>
       <c r="DD16" s="7"/>
       <c r="DE16" s="7"/>
       <c r="DF16" s="7"/>
@@ -4024,9 +4038,11 @@
         <v>453711.15566789632</v>
       </c>
       <c r="DB17" s="15">
-        <v>533298.22377584793</v>
-      </c>
-      <c r="DC17" s="7"/>
+        <v>526108.90505053825</v>
+      </c>
+      <c r="DC17" s="15">
+        <v>539553.61193208536</v>
+      </c>
       <c r="DD17" s="7"/>
       <c r="DE17" s="7"/>
       <c r="DF17" s="7"/>
@@ -4417,9 +4433,11 @@
         <v>73578.480825932318</v>
       </c>
       <c r="DB18" s="15">
-        <v>85883.023619640415</v>
-      </c>
-      <c r="DC18" s="7"/>
+        <v>91656.710132000793</v>
+      </c>
+      <c r="DC18" s="15">
+        <v>85097.540771346918</v>
+      </c>
       <c r="DD18" s="7"/>
       <c r="DE18" s="7"/>
       <c r="DF18" s="7"/>
@@ -4810,9 +4828,11 @@
         <v>17917.920810125586</v>
       </c>
       <c r="DB19" s="15">
-        <v>13314.121046315191</v>
-      </c>
-      <c r="DC19" s="7"/>
+        <v>15869.538775295068</v>
+      </c>
+      <c r="DC19" s="15">
+        <v>17583.524799366816</v>
+      </c>
       <c r="DD19" s="7"/>
       <c r="DE19" s="7"/>
       <c r="DF19" s="7"/>
@@ -4992,7 +5012,7 @@
       <c r="CZ20" s="21"/>
       <c r="DA20" s="21"/>
       <c r="DB20" s="21"/>
-      <c r="DC20" s="7"/>
+      <c r="DC20" s="21"/>
       <c r="DD20" s="7"/>
       <c r="DE20" s="7"/>
       <c r="DF20" s="7"/>
@@ -5383,9 +5403,11 @@
         <v>845148.31742199033</v>
       </c>
       <c r="DB21" s="14">
-        <v>1103102.7275759915</v>
-      </c>
-      <c r="DC21" s="7"/>
+        <v>1099667.4718996123</v>
+      </c>
+      <c r="DC21" s="14">
+        <v>1009603.1569701533</v>
+      </c>
       <c r="DD21" s="7"/>
       <c r="DE21" s="7"/>
       <c r="DF21" s="7"/>
@@ -5566,6 +5588,7 @@
       <c r="CZ22" s="22"/>
       <c r="DA22" s="22"/>
       <c r="DB22" s="22"/>
+      <c r="DC22" s="22"/>
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
@@ -5678,7 +5701,7 @@
       <c r="CZ24" s="21"/>
       <c r="DA24" s="21"/>
       <c r="DB24" s="21"/>
-      <c r="DC24" s="7"/>
+      <c r="DC24" s="21"/>
       <c r="DD24" s="7"/>
       <c r="DE24" s="7"/>
       <c r="DF24" s="7"/>
@@ -5858,7 +5881,7 @@
       <c r="CZ25" s="21"/>
       <c r="DA25" s="21"/>
       <c r="DB25" s="21"/>
-      <c r="DC25" s="7"/>
+      <c r="DC25" s="21"/>
       <c r="DD25" s="7"/>
       <c r="DE25" s="7"/>
       <c r="DF25" s="7"/>
@@ -5944,7 +5967,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5954,7 +5977,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6123,6 +6146,7 @@
       <c r="DB34" s="19">
         <v>2026</v>
       </c>
+      <c r="DC34" s="19"/>
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -6440,6 +6464,9 @@
       </c>
       <c r="DB35" s="16" t="s">
         <v>2</v>
+      </c>
+      <c r="DC35" s="16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6762,9 +6789,11 @@
         <v>45575.060517017955</v>
       </c>
       <c r="DB37" s="15">
-        <v>77398.912649426013</v>
-      </c>
-      <c r="DC37" s="7"/>
+        <v>76293.559509228828</v>
+      </c>
+      <c r="DC37" s="15">
+        <v>23171.993505084029</v>
+      </c>
       <c r="DD37" s="7"/>
       <c r="DE37" s="7"/>
       <c r="DF37" s="7"/>
@@ -7155,9 +7184,11 @@
         <v>878.61770689120135</v>
       </c>
       <c r="DB38" s="15">
-        <v>537.01507590044059</v>
-      </c>
-      <c r="DC38" s="7"/>
+        <v>818.86315687798185</v>
+      </c>
+      <c r="DC38" s="15">
+        <v>460.68174585717287</v>
+      </c>
       <c r="DD38" s="7"/>
       <c r="DE38" s="7"/>
       <c r="DF38" s="7"/>
@@ -7548,9 +7579,11 @@
         <v>76516.100932686037</v>
       </c>
       <c r="DB39" s="15">
-        <v>124198.89298361511</v>
-      </c>
-      <c r="DC39" s="7"/>
+        <v>124199.11359093894</v>
+      </c>
+      <c r="DC39" s="15">
+        <v>121078.7426258558</v>
+      </c>
       <c r="DD39" s="7"/>
       <c r="DE39" s="7"/>
       <c r="DF39" s="7"/>
@@ -7941,9 +7974,11 @@
         <v>5141.0222588246997</v>
       </c>
       <c r="DB40" s="15">
-        <v>4592.334449583479</v>
-      </c>
-      <c r="DC40" s="7"/>
+        <v>4649.4108032616377</v>
+      </c>
+      <c r="DC40" s="15">
+        <v>5080.9199662293022</v>
+      </c>
       <c r="DD40" s="7"/>
       <c r="DE40" s="7"/>
       <c r="DF40" s="7"/>
@@ -8334,9 +8369,11 @@
         <v>128639.39365782891</v>
       </c>
       <c r="DB41" s="15">
-        <v>175017.23262985493</v>
-      </c>
-      <c r="DC41" s="7"/>
+        <v>171834.14134515217</v>
+      </c>
+      <c r="DC41" s="15">
+        <v>148954.87770916149</v>
+      </c>
       <c r="DD41" s="7"/>
       <c r="DE41" s="7"/>
       <c r="DF41" s="7"/>
@@ -8727,9 +8764,11 @@
         <v>360931.83322930959</v>
       </c>
       <c r="DB42" s="15">
-        <v>419661.35771909857</v>
-      </c>
-      <c r="DC42" s="7"/>
+        <v>414000.58966404793</v>
+      </c>
+      <c r="DC42" s="15">
+        <v>405249.87352604943</v>
+      </c>
       <c r="DD42" s="7"/>
       <c r="DE42" s="7"/>
       <c r="DF42" s="7"/>
@@ -9120,9 +9159,11 @@
         <v>58861.991227136663</v>
       </c>
       <c r="DB43" s="15">
-        <v>66016.833538281644</v>
-      </c>
-      <c r="DC43" s="7"/>
+        <v>70454.969101333132</v>
+      </c>
+      <c r="DC43" s="15">
+        <v>63729.840114532977</v>
+      </c>
       <c r="DD43" s="7"/>
       <c r="DE43" s="7"/>
       <c r="DF43" s="7"/>
@@ -9513,9 +9554,11 @@
         <v>14648.389538574198</v>
       </c>
       <c r="DB44" s="15">
-        <v>10374.460937365184</v>
-      </c>
-      <c r="DC44" s="7"/>
+        <v>12359.833835081794</v>
+      </c>
+      <c r="DC44" s="15">
+        <v>13362.777768847194</v>
+      </c>
       <c r="DD44" s="7"/>
       <c r="DE44" s="7"/>
       <c r="DF44" s="7"/>
@@ -9695,7 +9738,7 @@
       <c r="CZ45" s="21"/>
       <c r="DA45" s="21"/>
       <c r="DB45" s="21"/>
-      <c r="DC45" s="7"/>
+      <c r="DC45" s="21"/>
       <c r="DD45" s="7"/>
       <c r="DE45" s="7"/>
       <c r="DF45" s="7"/>
@@ -10086,9 +10129,11 @@
         <v>691192.40906826931</v>
       </c>
       <c r="DB46" s="14">
-        <v>877797.03998312529</v>
-      </c>
-      <c r="DC46" s="7"/>
+        <v>874610.48100592243</v>
+      </c>
+      <c r="DC46" s="14">
+        <v>781089.70696161734</v>
+      </c>
       <c r="DD46" s="7"/>
       <c r="DE46" s="7"/>
       <c r="DF46" s="7"/>
@@ -10269,6 +10314,7 @@
       <c r="CZ47" s="22"/>
       <c r="DA47" s="22"/>
       <c r="DB47" s="22"/>
+      <c r="DC47" s="22"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
@@ -10381,7 +10427,7 @@
       <c r="CZ49" s="21"/>
       <c r="DA49" s="21"/>
       <c r="DB49" s="21"/>
-      <c r="DC49" s="7"/>
+      <c r="DC49" s="21"/>
       <c r="DD49" s="7"/>
       <c r="DE49" s="7"/>
       <c r="DF49" s="7"/>
@@ -10561,7 +10607,7 @@
       <c r="CZ50" s="21"/>
       <c r="DA50" s="21"/>
       <c r="DB50" s="21"/>
-      <c r="DC50" s="7"/>
+      <c r="DC50" s="21"/>
       <c r="DD50" s="7"/>
       <c r="DE50" s="7"/>
       <c r="DF50" s="7"/>
@@ -10647,7 +10693,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:179" x14ac:dyDescent="0.2">
@@ -10667,10 +10713,11 @@
       <c r="CZ55" s="23"/>
       <c r="DA55" s="23"/>
       <c r="DB55" s="23"/>
+      <c r="DC55" s="23"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CS56" s="23"/>
       <c r="CW56" s="23"/>
@@ -10684,12 +10731,13 @@
       <c r="CZ57" s="24"/>
       <c r="DA57" s="24"/>
       <c r="DB57" s="24"/>
+      <c r="DC57" s="24"/>
     </row>
     <row r="58" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CY58" s="24"/>
       <c r="CZ58" s="24"/>
       <c r="DA58" s="24"/>
       <c r="DB58" s="24"/>
+      <c r="DC58" s="24"/>
     </row>
     <row r="59" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -10844,12 +10892,13 @@
       <c r="CV59" s="19"/>
       <c r="CW59" s="19"/>
       <c r="CX59" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY59" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="CY59" s="19"/>
       <c r="CZ59" s="25"/>
       <c r="DA59" s="25"/>
       <c r="DB59" s="25"/>
+      <c r="DC59" s="25"/>
     </row>
     <row r="60" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
@@ -11156,17 +11205,20 @@
       <c r="CX60" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="CY60" s="26"/>
+      <c r="CY60" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
       <c r="DB60" s="26"/>
+      <c r="DC60" s="26"/>
     </row>
     <row r="61" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="CY61" s="24"/>
       <c r="CZ61" s="24"/>
       <c r="DA61" s="24"/>
       <c r="DB61" s="24"/>
+      <c r="DC61" s="24"/>
     </row>
     <row r="62" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
@@ -11473,13 +11525,15 @@
         <v>6.2109298478013812</v>
       </c>
       <c r="CX62" s="27">
-        <v>6.7616953389733112</v>
-      </c>
-      <c r="CY62" s="28"/>
+        <v>5.2370049892493</v>
+      </c>
+      <c r="CY62" s="27">
+        <v>-4.4772980194531584</v>
+      </c>
       <c r="CZ62" s="28"/>
       <c r="DA62" s="28"/>
       <c r="DB62" s="28"/>
-      <c r="DC62" s="7"/>
+      <c r="DC62" s="28"/>
       <c r="DD62" s="7"/>
       <c r="DE62" s="7"/>
       <c r="DF62" s="7"/>
@@ -11854,13 +11908,15 @@
         <v>25.010011005945444</v>
       </c>
       <c r="CX63" s="27">
-        <v>13.201838917001041</v>
-      </c>
-      <c r="CY63" s="28"/>
+        <v>72.614921516940257</v>
+      </c>
+      <c r="CY63" s="27">
+        <v>8.9810800685060883</v>
+      </c>
       <c r="CZ63" s="28"/>
       <c r="DA63" s="28"/>
       <c r="DB63" s="28"/>
-      <c r="DC63" s="7"/>
+      <c r="DC63" s="28"/>
       <c r="DD63" s="7"/>
       <c r="DE63" s="7"/>
       <c r="DF63" s="7"/>
@@ -12237,11 +12293,13 @@
       <c r="CX64" s="27">
         <v>2.5802979482211015</v>
       </c>
-      <c r="CY64" s="28"/>
+      <c r="CY64" s="27">
+        <v>20.167287172095811</v>
+      </c>
       <c r="CZ64" s="28"/>
       <c r="DA64" s="28"/>
       <c r="DB64" s="28"/>
-      <c r="DC64" s="7"/>
+      <c r="DC64" s="28"/>
       <c r="DD64" s="7"/>
       <c r="DE64" s="7"/>
       <c r="DF64" s="7"/>
@@ -12616,13 +12674,15 @@
         <v>11.833242040996225</v>
       </c>
       <c r="CX65" s="27">
-        <v>3.3598336594911729</v>
-      </c>
-      <c r="CY65" s="28"/>
+        <v>4.6444531676804957</v>
+      </c>
+      <c r="CY65" s="27">
+        <v>13.706728118184458</v>
+      </c>
       <c r="CZ65" s="28"/>
       <c r="DA65" s="28"/>
       <c r="DB65" s="28"/>
-      <c r="DC65" s="7"/>
+      <c r="DC65" s="28"/>
       <c r="DD65" s="7"/>
       <c r="DE65" s="7"/>
       <c r="DF65" s="7"/>
@@ -12997,13 +13057,15 @@
         <v>5.5078100348982133</v>
       </c>
       <c r="CX66" s="27">
-        <v>6.1756418428943221</v>
-      </c>
-      <c r="CY66" s="28"/>
+        <v>4.2416014741711905</v>
+      </c>
+      <c r="CY66" s="27">
+        <v>10.126104483040365</v>
+      </c>
       <c r="CZ66" s="28"/>
       <c r="DA66" s="28"/>
       <c r="DB66" s="28"/>
-      <c r="DC66" s="7"/>
+      <c r="DC66" s="28"/>
       <c r="DD66" s="7"/>
       <c r="DE66" s="7"/>
       <c r="DF66" s="7"/>
@@ -13378,13 +13440,15 @@
         <v>5.3312139218381986</v>
       </c>
       <c r="CX67" s="27">
-        <v>5.9890746699372528</v>
-      </c>
-      <c r="CY67" s="28"/>
+        <v>4.5602507863551835</v>
+      </c>
+      <c r="CY67" s="27">
+        <v>13.839906178331972</v>
+      </c>
       <c r="CZ67" s="28"/>
       <c r="DA67" s="28"/>
       <c r="DB67" s="28"/>
-      <c r="DC67" s="7"/>
+      <c r="DC67" s="28"/>
       <c r="DD67" s="7"/>
       <c r="DE67" s="7"/>
       <c r="DF67" s="7"/>
@@ -13759,13 +13823,15 @@
         <v>5.0416267907386469</v>
       </c>
       <c r="CX68" s="27">
-        <v>8.3138977321431895</v>
-      </c>
-      <c r="CY68" s="28"/>
+        <v>15.59555205776293</v>
+      </c>
+      <c r="CY68" s="27">
+        <v>13.13686721557869</v>
+      </c>
       <c r="CZ68" s="28"/>
       <c r="DA68" s="28"/>
       <c r="DB68" s="28"/>
-      <c r="DC68" s="7"/>
+      <c r="DC68" s="28"/>
       <c r="DD68" s="7"/>
       <c r="DE68" s="7"/>
       <c r="DF68" s="7"/>
@@ -14140,13 +14206,15 @@
         <v>18.365864065054225</v>
       </c>
       <c r="CX69" s="27">
-        <v>14.091495197807831</v>
-      </c>
-      <c r="CY69" s="28"/>
+        <v>35.989405584839375</v>
+      </c>
+      <c r="CY69" s="27">
+        <v>18.072010891202069</v>
+      </c>
       <c r="CZ69" s="28"/>
       <c r="DA69" s="28"/>
       <c r="DB69" s="28"/>
-      <c r="DC69" s="7"/>
+      <c r="DC69" s="28"/>
       <c r="DD69" s="7"/>
       <c r="DE69" s="7"/>
       <c r="DF69" s="7"/>
@@ -14318,11 +14386,11 @@
       <c r="CV70" s="21"/>
       <c r="CW70" s="21"/>
       <c r="CX70" s="21"/>
-      <c r="CY70" s="29"/>
+      <c r="CY70" s="21"/>
       <c r="CZ70" s="29"/>
       <c r="DA70" s="29"/>
       <c r="DB70" s="29"/>
-      <c r="DC70" s="7"/>
+      <c r="DC70" s="29"/>
       <c r="DD70" s="7"/>
       <c r="DE70" s="7"/>
       <c r="DF70" s="7"/>
@@ -14697,13 +14765,15 @@
         <v>3.7484300966110595</v>
       </c>
       <c r="CX71" s="27">
-        <v>5.8325793348113137</v>
-      </c>
-      <c r="CY71" s="28"/>
+        <v>5.5029980910910012</v>
+      </c>
+      <c r="CY71" s="27">
+        <v>13.467898755753069</v>
+      </c>
       <c r="CZ71" s="28"/>
       <c r="DA71" s="28"/>
       <c r="DB71" s="28"/>
-      <c r="DC71" s="7"/>
+      <c r="DC71" s="28"/>
       <c r="DD71" s="7"/>
       <c r="DE71" s="7"/>
       <c r="DF71" s="7"/>
@@ -14876,19 +14946,20 @@
       <c r="CV72" s="22"/>
       <c r="CW72" s="22"/>
       <c r="CX72" s="22"/>
-      <c r="CY72" s="30"/>
+      <c r="CY72" s="22"/>
       <c r="CZ72" s="30"/>
       <c r="DA72" s="30"/>
       <c r="DB72" s="30"/>
+      <c r="DC72" s="30"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="CY73" s="24"/>
       <c r="CZ73" s="24"/>
       <c r="DA73" s="24"/>
       <c r="DB73" s="24"/>
+      <c r="DC73" s="24"/>
     </row>
     <row r="74" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="7"/>
@@ -14992,11 +15063,11 @@
       <c r="CV74" s="21"/>
       <c r="CW74" s="21"/>
       <c r="CX74" s="21"/>
-      <c r="CY74" s="29"/>
+      <c r="CY74" s="21"/>
       <c r="CZ74" s="29"/>
       <c r="DA74" s="29"/>
       <c r="DB74" s="29"/>
-      <c r="DC74" s="7"/>
+      <c r="DC74" s="29"/>
       <c r="DD74" s="7"/>
       <c r="DE74" s="7"/>
       <c r="DF74" s="7"/>
@@ -15168,11 +15239,11 @@
       <c r="CV75" s="21"/>
       <c r="CW75" s="21"/>
       <c r="CX75" s="21"/>
-      <c r="CY75" s="29"/>
+      <c r="CY75" s="21"/>
       <c r="CZ75" s="29"/>
       <c r="DA75" s="29"/>
       <c r="DB75" s="29"/>
-      <c r="DC75" s="7"/>
+      <c r="DC75" s="29"/>
       <c r="DD75" s="7"/>
       <c r="DE75" s="7"/>
       <c r="DF75" s="7"/>
@@ -15246,67 +15317,67 @@
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CY76" s="24"/>
       <c r="CZ76" s="24"/>
       <c r="DA76" s="24"/>
       <c r="DB76" s="24"/>
+      <c r="DC76" s="24"/>
     </row>
     <row r="77" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CY77" s="24"/>
       <c r="CZ77" s="24"/>
       <c r="DA77" s="24"/>
       <c r="DB77" s="24"/>
+      <c r="DC77" s="24"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY78" s="24"/>
+        <v>57</v>
+      </c>
       <c r="CZ78" s="24"/>
       <c r="DA78" s="24"/>
       <c r="DB78" s="24"/>
+      <c r="DC78" s="24"/>
     </row>
     <row r="79" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY79" s="24"/>
       <c r="CZ79" s="24"/>
       <c r="DA79" s="24"/>
       <c r="DB79" s="24"/>
+      <c r="DC79" s="24"/>
     </row>
     <row r="80" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CY80" s="24"/>
       <c r="CZ80" s="24"/>
       <c r="DA80" s="24"/>
       <c r="DB80" s="24"/>
+      <c r="DC80" s="24"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="CY81" s="24"/>
+        <v>58</v>
+      </c>
       <c r="CZ81" s="24"/>
       <c r="DA81" s="24"/>
       <c r="DB81" s="24"/>
+      <c r="DC81" s="24"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CY82" s="24"/>
       <c r="CZ82" s="24"/>
       <c r="DA82" s="24"/>
       <c r="DB82" s="24"/>
+      <c r="DC82" s="24"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY83" s="24"/>
       <c r="CZ83" s="24"/>
       <c r="DA83" s="24"/>
       <c r="DB83" s="24"/>
+      <c r="DC83" s="24"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
@@ -15461,12 +15532,13 @@
       <c r="CV84" s="19"/>
       <c r="CW84" s="19"/>
       <c r="CX84" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY84" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="CY84" s="19"/>
       <c r="CZ84" s="25"/>
       <c r="DA84" s="25"/>
       <c r="DB84" s="25"/>
+      <c r="DC84" s="25"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
@@ -15773,17 +15845,20 @@
       <c r="CX85" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="CY85" s="30"/>
+      <c r="CY85" s="20" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ85" s="30"/>
       <c r="DA85" s="30"/>
       <c r="DB85" s="30"/>
+      <c r="DC85" s="30"/>
     </row>
     <row r="86" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="CY86" s="24"/>
       <c r="CZ86" s="24"/>
       <c r="DA86" s="24"/>
       <c r="DB86" s="24"/>
+      <c r="DC86" s="24"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -16090,13 +16165,15 @@
         <v>5.1741738290558033</v>
       </c>
       <c r="CX87" s="27">
-        <v>3.5358015507279248</v>
-      </c>
-      <c r="CY87" s="28"/>
+        <v>2.0571809932881138</v>
+      </c>
+      <c r="CY87" s="27">
+        <v>-10.65699353638955</v>
+      </c>
       <c r="CZ87" s="28"/>
       <c r="DA87" s="28"/>
       <c r="DB87" s="28"/>
-      <c r="DC87" s="7"/>
+      <c r="DC87" s="28"/>
       <c r="DD87" s="7"/>
       <c r="DE87" s="7"/>
       <c r="DF87" s="7"/>
@@ -16471,13 +16548,15 @@
         <v>22.281191730130317</v>
       </c>
       <c r="CX88" s="27">
-        <v>9.4427835878962725</v>
-      </c>
-      <c r="CY88" s="28"/>
+        <v>66.882955969216198</v>
+      </c>
+      <c r="CY88" s="27">
+        <v>1.3079277090901371</v>
+      </c>
       <c r="CZ88" s="28"/>
       <c r="DA88" s="28"/>
       <c r="DB88" s="28"/>
-      <c r="DC88" s="7"/>
+      <c r="DC88" s="28"/>
       <c r="DD88" s="7"/>
       <c r="DE88" s="7"/>
       <c r="DF88" s="7"/>
@@ -16852,13 +16931,15 @@
         <v>-11.206219332361727</v>
       </c>
       <c r="CX89" s="27">
-        <v>-0.12032865690188999</v>
-      </c>
-      <c r="CY89" s="28"/>
+        <v>-0.12015124640754493</v>
+      </c>
+      <c r="CY89" s="27">
+        <v>12.56274899195104</v>
+      </c>
       <c r="CZ89" s="28"/>
       <c r="DA89" s="28"/>
       <c r="DB89" s="28"/>
-      <c r="DC89" s="7"/>
+      <c r="DC89" s="28"/>
       <c r="DD89" s="7"/>
       <c r="DE89" s="7"/>
       <c r="DF89" s="7"/>
@@ -17233,13 +17314,15 @@
         <v>8.4750808576495587</v>
       </c>
       <c r="CX90" s="27">
-        <v>0.31107026315125097</v>
-      </c>
-      <c r="CY90" s="28"/>
+        <v>1.5577978669505654</v>
+      </c>
+      <c r="CY90" s="27">
+        <v>6.849111192760617</v>
+      </c>
       <c r="CZ90" s="28"/>
       <c r="DA90" s="28"/>
       <c r="DB90" s="28"/>
-      <c r="DC90" s="7"/>
+      <c r="DC90" s="28"/>
       <c r="DD90" s="7"/>
       <c r="DE90" s="7"/>
       <c r="DF90" s="7"/>
@@ -17614,13 +17697,15 @@
         <v>4.794919426554344</v>
       </c>
       <c r="CX91" s="27">
-        <v>5.3159470742307775</v>
-      </c>
-      <c r="CY91" s="28"/>
+        <v>3.4005341275457965</v>
+      </c>
+      <c r="CY91" s="27">
+        <v>9.034686309353603</v>
+      </c>
       <c r="CZ91" s="28"/>
       <c r="DA91" s="28"/>
       <c r="DB91" s="28"/>
-      <c r="DC91" s="7"/>
+      <c r="DC91" s="28"/>
       <c r="DD91" s="7"/>
       <c r="DE91" s="7"/>
       <c r="DF91" s="7"/>
@@ -17956,13 +18041,15 @@
         <v>3.0278252845553624</v>
       </c>
       <c r="CX92" s="27">
-        <v>2.4695311733247109</v>
-      </c>
-      <c r="CY92" s="28"/>
+        <v>1.0873304107035437</v>
+      </c>
+      <c r="CY92" s="27">
+        <v>5.8246530340351654</v>
+      </c>
       <c r="CZ92" s="28"/>
       <c r="DA92" s="28"/>
       <c r="DB92" s="28"/>
-      <c r="DC92" s="7"/>
+      <c r="DC92" s="28"/>
       <c r="DD92" s="7"/>
       <c r="DE92" s="7"/>
       <c r="DF92" s="7"/>
@@ -18298,13 +18385,15 @@
         <v>2.748693499692763</v>
       </c>
       <c r="CX93" s="27">
-        <v>4.717154619298114</v>
-      </c>
-      <c r="CY93" s="28"/>
+        <v>11.757009502794929</v>
+      </c>
+      <c r="CY93" s="27">
+        <v>5.1711137190411023</v>
+      </c>
       <c r="CZ93" s="28"/>
       <c r="DA93" s="28"/>
       <c r="DB93" s="28"/>
-      <c r="DC93" s="7"/>
+      <c r="DC93" s="28"/>
       <c r="DD93" s="7"/>
       <c r="DE93" s="7"/>
       <c r="DF93" s="7"/>
@@ -18679,13 +18768,15 @@
         <v>16.272248876773233</v>
       </c>
       <c r="CX94" s="27">
-        <v>10.241181240563193</v>
-      </c>
-      <c r="CY94" s="28"/>
+        <v>31.338166883353182</v>
+      </c>
+      <c r="CY94" s="27">
+        <v>10.873564716854304</v>
+      </c>
       <c r="CZ94" s="28"/>
       <c r="DA94" s="28"/>
       <c r="DB94" s="28"/>
-      <c r="DC94" s="7"/>
+      <c r="DC94" s="28"/>
       <c r="DD94" s="7"/>
       <c r="DE94" s="7"/>
       <c r="DF94" s="7"/>
@@ -18857,11 +18948,11 @@
       <c r="CV95" s="21"/>
       <c r="CW95" s="21"/>
       <c r="CX95" s="21"/>
-      <c r="CY95" s="29"/>
+      <c r="CY95" s="21"/>
       <c r="CZ95" s="29"/>
       <c r="DA95" s="29"/>
       <c r="DB95" s="29"/>
-      <c r="DC95" s="7"/>
+      <c r="DC95" s="29"/>
       <c r="DD95" s="7"/>
       <c r="DE95" s="7"/>
       <c r="DF95" s="7"/>
@@ -19236,13 +19327,15 @@
         <v>1.9566995412859853</v>
       </c>
       <c r="CX96" s="27">
-        <v>2.984648708335186</v>
-      </c>
-      <c r="CY96" s="28"/>
+        <v>2.610796163945281</v>
+      </c>
+      <c r="CY96" s="27">
+        <v>6.8643273977524899</v>
+      </c>
       <c r="CZ96" s="28"/>
       <c r="DA96" s="28"/>
       <c r="DB96" s="28"/>
-      <c r="DC96" s="7"/>
+      <c r="DC96" s="28"/>
       <c r="DD96" s="7"/>
       <c r="DE96" s="7"/>
       <c r="DF96" s="7"/>
@@ -19415,19 +19508,20 @@
       <c r="CV97" s="22"/>
       <c r="CW97" s="22"/>
       <c r="CX97" s="22"/>
-      <c r="CY97" s="30"/>
+      <c r="CY97" s="22"/>
       <c r="CZ97" s="30"/>
       <c r="DA97" s="30"/>
       <c r="DB97" s="30"/>
+      <c r="DC97" s="30"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A98" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="CY98" s="24"/>
       <c r="CZ98" s="24"/>
       <c r="DA98" s="24"/>
       <c r="DB98" s="24"/>
+      <c r="DC98" s="24"/>
     </row>
     <row r="99" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="7"/>
@@ -19531,11 +19625,11 @@
       <c r="CV99" s="21"/>
       <c r="CW99" s="21"/>
       <c r="CX99" s="21"/>
-      <c r="CY99" s="29"/>
+      <c r="CY99" s="21"/>
       <c r="CZ99" s="29"/>
       <c r="DA99" s="29"/>
       <c r="DB99" s="29"/>
-      <c r="DC99" s="7"/>
+      <c r="DC99" s="29"/>
       <c r="DD99" s="7"/>
       <c r="DE99" s="7"/>
       <c r="DF99" s="7"/>
@@ -19711,7 +19805,7 @@
       <c r="CZ100" s="29"/>
       <c r="DA100" s="29"/>
       <c r="DB100" s="29"/>
-      <c r="DC100" s="7"/>
+      <c r="DC100" s="29"/>
       <c r="DD100" s="7"/>
       <c r="DE100" s="7"/>
       <c r="DF100" s="7"/>
@@ -19788,7 +19882,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19798,7 +19892,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -19967,6 +20061,7 @@
       <c r="DB108" s="19">
         <v>2026</v>
       </c>
+      <c r="DC108" s="19"/>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
@@ -20284,6 +20379,9 @@
       </c>
       <c r="DB109" s="16" t="s">
         <v>2</v>
+      </c>
+      <c r="DC109" s="16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20606,9 +20704,11 @@
         <v>135.78737904615701</v>
       </c>
       <c r="DB111" s="27">
-        <v>147.16317590058858</v>
-      </c>
-      <c r="DC111" s="7"/>
+        <v>147.16317590058856</v>
+      </c>
+      <c r="DC111" s="27">
+        <v>151.6713556495375</v>
+      </c>
       <c r="DD111" s="7"/>
       <c r="DE111" s="7"/>
       <c r="DF111" s="7"/>
@@ -21001,7 +21101,9 @@
       <c r="DB112" s="27">
         <v>128.71391092160843</v>
       </c>
-      <c r="DC112" s="7"/>
+      <c r="DC112" s="27">
+        <v>133.63325669695612</v>
+      </c>
       <c r="DD112" s="7"/>
       <c r="DE112" s="7"/>
       <c r="DF112" s="7"/>
@@ -21392,9 +21494,11 @@
         <v>124.88518373611642</v>
       </c>
       <c r="DB113" s="27">
-        <v>132.49742372293346</v>
-      </c>
-      <c r="DC113" s="7"/>
+        <v>132.49718837582657</v>
+      </c>
+      <c r="DC113" s="27">
+        <v>136.96592082444297</v>
+      </c>
       <c r="DD113" s="7"/>
       <c r="DE113" s="7"/>
       <c r="DF113" s="7"/>
@@ -21787,7 +21891,9 @@
       <c r="DB114" s="27">
         <v>125.25192360457086</v>
       </c>
-      <c r="DC114" s="7"/>
+      <c r="DC114" s="27">
+        <v>129.14173734520205</v>
+      </c>
       <c r="DD114" s="7"/>
       <c r="DE114" s="7"/>
       <c r="DF114" s="7"/>
@@ -22178,9 +22284,11 @@
         <v>104.89923516440609</v>
       </c>
       <c r="DB115" s="27">
-        <v>106.10448156321198</v>
-      </c>
-      <c r="DC115" s="7"/>
+        <v>106.10143628954928</v>
+      </c>
+      <c r="DC115" s="27">
+        <v>106.8842982103382</v>
+      </c>
       <c r="DD115" s="7"/>
       <c r="DE115" s="7"/>
       <c r="DF115" s="7"/>
@@ -22571,9 +22679,11 @@
         <v>125.7054972426446</v>
       </c>
       <c r="DB116" s="27">
-        <v>127.07822961694093</v>
-      </c>
-      <c r="DC116" s="7"/>
+        <v>127.07926466420341</v>
+      </c>
+      <c r="DC116" s="27">
+        <v>133.14096985088952</v>
+      </c>
       <c r="DD116" s="7"/>
       <c r="DE116" s="7"/>
       <c r="DF116" s="7"/>
@@ -22966,7 +23076,9 @@
       <c r="DB117" s="27">
         <v>130.09261277252691</v>
       </c>
-      <c r="DC117" s="7"/>
+      <c r="DC117" s="27">
+        <v>133.52856466988254</v>
+      </c>
       <c r="DD117" s="7"/>
       <c r="DE117" s="7"/>
       <c r="DF117" s="7"/>
@@ -23357,9 +23469,11 @@
         <v>122.32007322676392</v>
       </c>
       <c r="DB118" s="27">
-        <v>128.33554559314382</v>
-      </c>
-      <c r="DC118" s="7"/>
+        <v>128.39605278714532</v>
+      </c>
+      <c r="DC118" s="27">
+        <v>131.58585066317201</v>
+      </c>
       <c r="DD118" s="7"/>
       <c r="DE118" s="7"/>
       <c r="DF118" s="7"/>
@@ -23539,7 +23653,7 @@
       <c r="CZ119" s="21"/>
       <c r="DA119" s="21"/>
       <c r="DB119" s="21"/>
-      <c r="DC119" s="7"/>
+      <c r="DC119" s="21"/>
       <c r="DD119" s="7"/>
       <c r="DE119" s="7"/>
       <c r="DF119" s="7"/>
@@ -23930,9 +24044,11 @@
         <v>122.27395821103624</v>
       </c>
       <c r="DB120" s="27">
-        <v>125.66717331345723</v>
-      </c>
-      <c r="DC120" s="7"/>
+        <v>125.73225404694939</v>
+      </c>
+      <c r="DC120" s="27">
+        <v>129.255724146902</v>
+      </c>
       <c r="DD120" s="7"/>
       <c r="DE120" s="7"/>
       <c r="DF120" s="7"/>
@@ -24113,6 +24229,7 @@
       <c r="CZ121" s="22"/>
       <c r="DA121" s="22"/>
       <c r="DB121" s="22"/>
+      <c r="DC121" s="22"/>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="s">
@@ -24131,7 +24248,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24141,7 +24258,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24310,6 +24427,7 @@
       <c r="DB133" s="19">
         <v>2026</v>
       </c>
+      <c r="DC133" s="19"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
@@ -24627,6 +24745,9 @@
       </c>
       <c r="DB134" s="16" t="s">
         <v>2</v>
+      </c>
+      <c r="DC134" s="16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24949,9 +25070,11 @@
         <v>7.322404706848487</v>
       </c>
       <c r="DB136" s="17">
-        <v>10.325665517817431</v>
-      </c>
-      <c r="DC136" s="7"/>
+        <v>10.209997844842702</v>
+      </c>
+      <c r="DC136" s="17">
+        <v>3.4810981361880509</v>
+      </c>
       <c r="DD136" s="7"/>
       <c r="DE136" s="7"/>
       <c r="DF136" s="7"/>
@@ -25342,9 +25465,11 @@
         <v>0.12786826083711939</v>
       </c>
       <c r="DB137" s="17">
-        <v>6.2660810199336961E-2</v>
-      </c>
-      <c r="DC137" s="7"/>
+        <v>9.5846319114367168E-2</v>
+      </c>
+      <c r="DC137" s="17">
+        <v>6.0976831911346181E-2</v>
+      </c>
       <c r="DD137" s="7"/>
       <c r="DE137" s="7"/>
       <c r="DF137" s="7"/>
@@ -25735,9 +25860,11 @@
         <v>11.306568476522756</v>
       </c>
       <c r="DB138" s="17">
-        <v>14.917951826418344</v>
-      </c>
-      <c r="DC138" s="7"/>
+        <v>14.964554076645067</v>
+      </c>
+      <c r="DC138" s="17">
+        <v>16.425920780382754</v>
+      </c>
       <c r="DD138" s="7"/>
       <c r="DE138" s="7"/>
       <c r="DF138" s="7"/>
@@ -26128,9 +26255,11 @@
         <v>0.76624304280227507</v>
       </c>
       <c r="DB139" s="17">
-        <v>0.52143713297657868</v>
-      </c>
-      <c r="DC139" s="7"/>
+        <v>0.52956703877984224</v>
+      </c>
+      <c r="DC139" s="17">
+        <v>0.6499175712959615</v>
+      </c>
       <c r="DD139" s="7"/>
       <c r="DE139" s="7"/>
       <c r="DF139" s="7"/>
@@ -26521,9 +26650,11 @@
         <v>15.966634173610309</v>
       </c>
       <c r="DB140" s="17">
-        <v>16.834436420645645</v>
-      </c>
-      <c r="DC140" s="7"/>
+        <v>16.579420294034524</v>
+      </c>
+      <c r="DC140" s="17">
+        <v>15.769500579544188</v>
+      </c>
       <c r="DD140" s="7"/>
       <c r="DE140" s="7"/>
       <c r="DF140" s="7"/>
@@ -26914,9 +27045,11 @@
         <v>53.6842050460303</v>
       </c>
       <c r="DB141" s="17">
-        <v>48.345291009092314</v>
-      </c>
-      <c r="DC141" s="7"/>
+        <v>47.842544996053704</v>
+      </c>
+      <c r="DC141" s="17">
+        <v>53.442147858501208</v>
+      </c>
       <c r="DD141" s="7"/>
       <c r="DE141" s="7"/>
       <c r="DF141" s="7"/>
@@ -27307,9 +27440,11 @@
         <v>8.7059844182584953</v>
       </c>
       <c r="DB142" s="17">
-        <v>7.785587096531227</v>
-      </c>
-      <c r="DC142" s="7"/>
+        <v>8.334947834154729</v>
+      </c>
+      <c r="DC142" s="17">
+        <v>8.4288108831520461</v>
+      </c>
       <c r="DD142" s="7"/>
       <c r="DE142" s="7"/>
       <c r="DF142" s="7"/>
@@ -27700,9 +27835,11 @@
         <v>2.1200918750902518</v>
       </c>
       <c r="DB143" s="17">
-        <v>1.2069701863191156</v>
-      </c>
-      <c r="DC143" s="7"/>
+        <v>1.4431215963750708</v>
+      </c>
+      <c r="DC143" s="17">
+        <v>1.7416273590244562</v>
+      </c>
       <c r="DD143" s="7"/>
       <c r="DE143" s="7"/>
       <c r="DF143" s="7"/>
@@ -27882,7 +28019,7 @@
       <c r="CZ144" s="21"/>
       <c r="DA144" s="21"/>
       <c r="DB144" s="21"/>
-      <c r="DC144" s="7"/>
+      <c r="DC144" s="21"/>
       <c r="DD144" s="7"/>
       <c r="DE144" s="7"/>
       <c r="DF144" s="7"/>
@@ -28275,7 +28412,9 @@
       <c r="DB145" s="27">
         <v>100</v>
       </c>
-      <c r="DC145" s="7"/>
+      <c r="DC145" s="27">
+        <v>100</v>
+      </c>
       <c r="DD145" s="7"/>
       <c r="DE145" s="7"/>
       <c r="DF145" s="7"/>
@@ -28456,6 +28595,7 @@
       <c r="CZ146" s="22"/>
       <c r="DA146" s="22"/>
       <c r="DB146" s="22"/>
+      <c r="DC146" s="22"/>
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
@@ -28568,7 +28708,7 @@
       <c r="CZ148" s="21"/>
       <c r="DA148" s="21"/>
       <c r="DB148" s="21"/>
-      <c r="DC148" s="7"/>
+      <c r="DC148" s="21"/>
       <c r="DD148" s="7"/>
       <c r="DE148" s="7"/>
       <c r="DF148" s="7"/>
@@ -28748,7 +28888,7 @@
       <c r="CZ149" s="21"/>
       <c r="DA149" s="21"/>
       <c r="DB149" s="21"/>
-      <c r="DC149" s="7"/>
+      <c r="DC149" s="21"/>
       <c r="DD149" s="7"/>
       <c r="DE149" s="7"/>
       <c r="DF149" s="7"/>
@@ -28834,7 +28974,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28844,7 +28984,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -29013,6 +29153,7 @@
       <c r="DB158" s="19">
         <v>2026</v>
       </c>
+      <c r="DC158" s="19"/>
     </row>
     <row r="159" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
@@ -29330,6 +29471,9 @@
       </c>
       <c r="DB159" s="16" t="s">
         <v>2</v>
+      </c>
+      <c r="DC159" s="16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -29652,9 +29796,11 @@
         <v>6.5936864929482306</v>
       </c>
       <c r="DB161" s="17">
-        <v>8.8174041519795878</v>
-      </c>
-      <c r="DC161" s="7"/>
+        <v>8.7231471799286844</v>
+      </c>
+      <c r="DC161" s="17">
+        <v>2.9666238459627658</v>
+      </c>
       <c r="DD161" s="7"/>
       <c r="DE161" s="7"/>
       <c r="DF161" s="7"/>
@@ -30045,9 +30191,11 @@
         <v>0.12711622630167224</v>
       </c>
       <c r="DB162" s="17">
-        <v>6.1177590199069723E-2</v>
-      </c>
-      <c r="DC162" s="7"/>
+        <v>9.3626039781295162E-2</v>
+      </c>
+      <c r="DC162" s="17">
+        <v>5.8979364566099798E-2</v>
+      </c>
       <c r="DD162" s="7"/>
       <c r="DE162" s="7"/>
       <c r="DF162" s="7"/>
@@ -30438,9 +30586,11 @@
         <v>11.070159325943713</v>
       </c>
       <c r="DB163" s="17">
-        <v>14.14893048465995</v>
-      </c>
-      <c r="DC163" s="7"/>
+        <v>14.200505972452202</v>
+      </c>
+      <c r="DC163" s="17">
+        <v>15.501259528414909</v>
+      </c>
       <c r="DD163" s="7"/>
       <c r="DE163" s="7"/>
       <c r="DF163" s="7"/>
@@ -30831,9 +30981,11 @@
         <v>0.7437903239931154</v>
       </c>
       <c r="DB164" s="17">
-        <v>0.52316586185706004</v>
-      </c>
-      <c r="DC164" s="7"/>
+        <v>0.53159788319872125</v>
+      </c>
+      <c r="DC164" s="17">
+        <v>0.65049122027144801</v>
+      </c>
       <c r="DD164" s="7"/>
       <c r="DE164" s="7"/>
       <c r="DF164" s="7"/>
@@ -31224,9 +31376,11 @@
         <v>18.611227781166669</v>
       </c>
       <c r="DB165" s="17">
-        <v>19.938234541462961</v>
-      </c>
-      <c r="DC165" s="7"/>
+        <v>19.646933700991013</v>
+      </c>
+      <c r="DC165" s="17">
+        <v>19.070137063844463</v>
+      </c>
       <c r="DD165" s="7"/>
       <c r="DE165" s="7"/>
       <c r="DF165" s="7"/>
@@ -31617,9 +31771,11 @@
         <v>52.218720647677173</v>
       </c>
       <c r="DB166" s="17">
-        <v>47.808472642738245</v>
-      </c>
-      <c r="DC166" s="7"/>
+        <v>47.335425158396262</v>
+      </c>
+      <c r="DC166" s="17">
+        <v>51.882628834329701</v>
+      </c>
       <c r="DD166" s="7"/>
       <c r="DE166" s="7"/>
       <c r="DF166" s="7"/>
@@ -32010,9 +32166,11 @@
         <v>8.51600660754983</v>
       </c>
       <c r="DB167" s="17">
-        <v>7.5207400493798371</v>
-      </c>
-      <c r="DC167" s="7"/>
+        <v>8.0555825286132201</v>
+      </c>
+      <c r="DC167" s="17">
+        <v>8.159093577412186</v>
+      </c>
       <c r="DD167" s="7"/>
       <c r="DE167" s="7"/>
       <c r="DF167" s="7"/>
@@ -32403,9 +32561,11 @@
         <v>2.1192925944195911</v>
       </c>
       <c r="DB168" s="17">
-        <v>1.1818746777232947</v>
-      </c>
-      <c r="DC168" s="7"/>
+        <v>1.4131815366386056</v>
+      </c>
+      <c r="DC168" s="17">
+        <v>1.7107865651984375</v>
+      </c>
       <c r="DD168" s="7"/>
       <c r="DE168" s="7"/>
       <c r="DF168" s="7"/>
@@ -32585,7 +32745,7 @@
       <c r="CZ169" s="21"/>
       <c r="DA169" s="21"/>
       <c r="DB169" s="21"/>
-      <c r="DC169" s="7"/>
+      <c r="DC169" s="21"/>
       <c r="DD169" s="7"/>
       <c r="DE169" s="7"/>
       <c r="DF169" s="7"/>
@@ -32978,7 +33138,9 @@
       <c r="DB170" s="27">
         <v>100</v>
       </c>
-      <c r="DC170" s="7"/>
+      <c r="DC170" s="27">
+        <v>100</v>
+      </c>
       <c r="DD170" s="7"/>
       <c r="DE170" s="7"/>
       <c r="DF170" s="7"/>
@@ -33159,6 +33321,7 @@
       <c r="CZ171" s="22"/>
       <c r="DA171" s="22"/>
       <c r="DB171" s="22"/>
+      <c r="DC171" s="22"/>
     </row>
     <row r="172" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A172" s="10" t="s">
@@ -33272,7 +33435,7 @@
       <c r="CZ173" s="31"/>
       <c r="DA173" s="31"/>
       <c r="DB173" s="31"/>
-      <c r="DC173" s="12"/>
+      <c r="DC173" s="31"/>
       <c r="DD173" s="12"/>
       <c r="DE173" s="12"/>
       <c r="DF173" s="12"/>
@@ -33352,10 +33515,10 @@
       <c r="CV174" s="23"/>
       <c r="CW174" s="24"/>
       <c r="CX174" s="24"/>
-      <c r="CY174" s="24"/>
       <c r="CZ174" s="24"/>
       <c r="DA174" s="24"/>
       <c r="DB174" s="24"/>
+      <c r="DC174" s="24"/>
     </row>
     <row r="175" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT175" s="23"/>
@@ -33367,15 +33530,32 @@
       <c r="CZ175" s="24"/>
       <c r="DA175" s="24"/>
       <c r="DB175" s="24"/>
+      <c r="DC175" s="24"/>
+    </row>
+    <row r="176" spans="1:179" x14ac:dyDescent="0.2">
+      <c r="CX176" s="24"/>
+      <c r="CY176" s="24"/>
+      <c r="CZ176" s="24"/>
+      <c r="DA176" s="24"/>
+      <c r="DB176" s="24"/>
+      <c r="DC176" s="24"/>
+    </row>
+    <row r="177" spans="102:107" x14ac:dyDescent="0.2">
+      <c r="CX177" s="24"/>
+      <c r="CY177" s="24"/>
+      <c r="CZ177" s="24"/>
+      <c r="DA177" s="24"/>
+      <c r="DB177" s="24"/>
+      <c r="DC177" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="50" max="105" man="1"/>
-    <brk id="100" max="105" man="1"/>
-    <brk id="124" max="105" man="1"/>
+    <brk id="50" max="106" man="1"/>
+    <brk id="100" max="106" man="1"/>
+    <brk id="124" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>